--- a/AAII_Financials/Yearly/IIJIY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IIJIY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -720,25 +720,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1678000</v>
+        <v>1703300</v>
       </c>
       <c r="E8" s="3">
-        <v>1502900</v>
+        <v>1525500</v>
       </c>
       <c r="F8" s="3">
-        <v>1414300</v>
+        <v>1435600</v>
       </c>
       <c r="G8" s="3">
-        <v>1357700</v>
+        <v>1378200</v>
       </c>
       <c r="H8" s="3">
-        <v>1277700</v>
+        <v>1297000</v>
       </c>
       <c r="I8" s="3">
-        <v>1170200</v>
+        <v>1187800</v>
       </c>
       <c r="J8" s="3">
-        <v>1047700</v>
+        <v>1063500</v>
       </c>
       <c r="K8" s="3">
         <v>1033800</v>
@@ -759,25 +759,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1293500</v>
+        <v>1313000</v>
       </c>
       <c r="E9" s="3">
-        <v>1160100</v>
+        <v>1177500</v>
       </c>
       <c r="F9" s="3">
-        <v>1146900</v>
+        <v>1164100</v>
       </c>
       <c r="G9" s="3">
-        <v>1141300</v>
+        <v>1158500</v>
       </c>
       <c r="H9" s="3">
-        <v>1085300</v>
+        <v>1101700</v>
       </c>
       <c r="I9" s="3">
-        <v>1947600</v>
+        <v>1977000</v>
       </c>
       <c r="J9" s="3">
-        <v>880100</v>
+        <v>893300</v>
       </c>
       <c r="K9" s="3">
         <v>852500</v>
@@ -798,25 +798,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>384500</v>
+        <v>390300</v>
       </c>
       <c r="E10" s="3">
-        <v>342800</v>
+        <v>348000</v>
       </c>
       <c r="F10" s="3">
-        <v>267500</v>
+        <v>271500</v>
       </c>
       <c r="G10" s="3">
-        <v>216400</v>
+        <v>219700</v>
       </c>
       <c r="H10" s="3">
-        <v>192400</v>
+        <v>195300</v>
       </c>
       <c r="I10" s="3">
-        <v>-777400</v>
+        <v>-789100</v>
       </c>
       <c r="J10" s="3">
-        <v>167600</v>
+        <v>170200</v>
       </c>
       <c r="K10" s="3">
         <v>181200</v>
@@ -854,22 +854,22 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="E12" s="3">
         <v>3400</v>
       </c>
       <c r="F12" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="G12" s="3">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="H12" s="3">
         <v>3000</v>
       </c>
       <c r="I12" s="3">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="J12" s="3">
         <v>3100</v>
@@ -935,7 +935,7 @@
         <v>2000</v>
       </c>
       <c r="E14" s="3">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F14" s="3">
         <v>2700</v>
@@ -944,7 +944,7 @@
         <v>1200</v>
       </c>
       <c r="H14" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="I14" s="3">
         <v>1500</v>
@@ -971,22 +971,22 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>20400</v>
+        <v>20800</v>
       </c>
       <c r="E15" s="3">
-        <v>20800</v>
+        <v>21100</v>
       </c>
       <c r="F15" s="3">
-        <v>18800</v>
+        <v>19100</v>
       </c>
       <c r="G15" s="3">
-        <v>18900</v>
+        <v>19100</v>
       </c>
       <c r="H15" s="3">
-        <v>8500</v>
+        <v>8600</v>
       </c>
       <c r="I15" s="3">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>10</v>
@@ -1024,25 +1024,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1497200</v>
+        <v>1519800</v>
       </c>
       <c r="E17" s="3">
-        <v>1354400</v>
+        <v>1374800</v>
       </c>
       <c r="F17" s="3">
-        <v>1317400</v>
+        <v>1337300</v>
       </c>
       <c r="G17" s="3">
-        <v>1300600</v>
+        <v>1320200</v>
       </c>
       <c r="H17" s="3">
-        <v>1237700</v>
+        <v>1256400</v>
       </c>
       <c r="I17" s="3">
-        <v>1125200</v>
+        <v>1142200</v>
       </c>
       <c r="J17" s="3">
-        <v>1013800</v>
+        <v>1029100</v>
       </c>
       <c r="K17" s="3">
         <v>988700</v>
@@ -1063,25 +1063,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>180700</v>
+        <v>183500</v>
       </c>
       <c r="E18" s="3">
-        <v>148500</v>
+        <v>150700</v>
       </c>
       <c r="F18" s="3">
-        <v>96900</v>
+        <v>98400</v>
       </c>
       <c r="G18" s="3">
-        <v>57100</v>
+        <v>58000</v>
       </c>
       <c r="H18" s="3">
-        <v>40000</v>
+        <v>40600</v>
       </c>
       <c r="I18" s="3">
-        <v>45000</v>
+        <v>45600</v>
       </c>
       <c r="J18" s="3">
-        <v>33900</v>
+        <v>34400</v>
       </c>
       <c r="K18" s="3">
         <v>45000</v>
@@ -1122,19 +1122,19 @@
         <v>3900</v>
       </c>
       <c r="E20" s="3">
-        <v>15300</v>
+        <v>15600</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>-5800</v>
+        <v>-5900</v>
       </c>
       <c r="H20" s="3">
         <v>1700</v>
       </c>
       <c r="I20" s="3">
-        <v>5900</v>
+        <v>6000</v>
       </c>
       <c r="J20" s="3">
         <v>4200</v>
@@ -1158,25 +1158,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>375000</v>
+        <v>382400</v>
       </c>
       <c r="E21" s="3">
-        <v>351900</v>
+        <v>358900</v>
       </c>
       <c r="F21" s="3">
-        <v>281800</v>
+        <v>287700</v>
       </c>
       <c r="G21" s="3">
-        <v>239800</v>
+        <v>245100</v>
       </c>
       <c r="H21" s="3">
-        <v>145000</v>
+        <v>148100</v>
       </c>
       <c r="I21" s="3">
-        <v>139500</v>
+        <v>142400</v>
       </c>
       <c r="J21" s="3">
-        <v>110100</v>
+        <v>112400</v>
       </c>
       <c r="K21" s="3">
         <v>119500</v>
@@ -1200,7 +1200,7 @@
         <v>3300</v>
       </c>
       <c r="E22" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="F22" s="3">
         <v>3700</v>
@@ -1212,7 +1212,7 @@
         <v>2900</v>
       </c>
       <c r="I22" s="3">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="J22" s="3">
         <v>2000</v>
@@ -1236,25 +1236,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>181300</v>
+        <v>184100</v>
       </c>
       <c r="E23" s="3">
-        <v>160400</v>
+        <v>162900</v>
       </c>
       <c r="F23" s="3">
-        <v>93200</v>
+        <v>94600</v>
       </c>
       <c r="G23" s="3">
-        <v>47500</v>
+        <v>48300</v>
       </c>
       <c r="H23" s="3">
-        <v>38800</v>
+        <v>39400</v>
       </c>
       <c r="I23" s="3">
-        <v>45600</v>
+        <v>46300</v>
       </c>
       <c r="J23" s="3">
-        <v>36000</v>
+        <v>36600</v>
       </c>
       <c r="K23" s="3">
         <v>45500</v>
@@ -1275,25 +1275,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>55300</v>
+        <v>56100</v>
       </c>
       <c r="E24" s="3">
-        <v>55500</v>
+        <v>56400</v>
       </c>
       <c r="F24" s="3">
-        <v>28100</v>
+        <v>28500</v>
       </c>
       <c r="G24" s="3">
-        <v>19700</v>
+        <v>20000</v>
       </c>
       <c r="H24" s="3">
-        <v>14200</v>
+        <v>14500</v>
       </c>
       <c r="I24" s="3">
-        <v>15300</v>
+        <v>15500</v>
       </c>
       <c r="J24" s="3">
-        <v>14800</v>
+        <v>15000</v>
       </c>
       <c r="K24" s="3">
         <v>16000</v>
@@ -1353,25 +1353,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>126000</v>
+        <v>127900</v>
       </c>
       <c r="E26" s="3">
-        <v>104900</v>
+        <v>106500</v>
       </c>
       <c r="F26" s="3">
-        <v>65100</v>
+        <v>66100</v>
       </c>
       <c r="G26" s="3">
-        <v>27800</v>
+        <v>28300</v>
       </c>
       <c r="H26" s="3">
-        <v>24600</v>
+        <v>24900</v>
       </c>
       <c r="I26" s="3">
-        <v>30400</v>
+        <v>30800</v>
       </c>
       <c r="J26" s="3">
-        <v>21300</v>
+        <v>21600</v>
       </c>
       <c r="K26" s="3">
         <v>29500</v>
@@ -1392,25 +1392,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>125100</v>
+        <v>127000</v>
       </c>
       <c r="E27" s="3">
-        <v>104100</v>
+        <v>105600</v>
       </c>
       <c r="F27" s="3">
-        <v>64500</v>
+        <v>65500</v>
       </c>
       <c r="G27" s="3">
-        <v>26600</v>
+        <v>27000</v>
       </c>
       <c r="H27" s="3">
-        <v>23400</v>
+        <v>23700</v>
       </c>
       <c r="I27" s="3">
-        <v>30100</v>
+        <v>30600</v>
       </c>
       <c r="J27" s="3">
-        <v>21000</v>
+        <v>21300</v>
       </c>
       <c r="K27" s="3">
         <v>29700</v>
@@ -1590,19 +1590,19 @@
         <v>-3900</v>
       </c>
       <c r="E32" s="3">
-        <v>-15300</v>
+        <v>-15600</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>5800</v>
+        <v>5900</v>
       </c>
       <c r="H32" s="3">
         <v>-1700</v>
       </c>
       <c r="I32" s="3">
-        <v>-5900</v>
+        <v>-6000</v>
       </c>
       <c r="J32" s="3">
         <v>-4200</v>
@@ -1626,25 +1626,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>125100</v>
+        <v>127000</v>
       </c>
       <c r="E33" s="3">
-        <v>104100</v>
+        <v>105600</v>
       </c>
       <c r="F33" s="3">
-        <v>64500</v>
+        <v>65500</v>
       </c>
       <c r="G33" s="3">
-        <v>26600</v>
+        <v>27000</v>
       </c>
       <c r="H33" s="3">
-        <v>23400</v>
+        <v>23700</v>
       </c>
       <c r="I33" s="3">
-        <v>30300</v>
+        <v>30700</v>
       </c>
       <c r="J33" s="3">
-        <v>21000</v>
+        <v>21300</v>
       </c>
       <c r="K33" s="3">
         <v>29700</v>
@@ -1704,25 +1704,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>125100</v>
+        <v>127000</v>
       </c>
       <c r="E35" s="3">
-        <v>104100</v>
+        <v>105600</v>
       </c>
       <c r="F35" s="3">
-        <v>64500</v>
+        <v>65500</v>
       </c>
       <c r="G35" s="3">
-        <v>26600</v>
+        <v>27000</v>
       </c>
       <c r="H35" s="3">
-        <v>23400</v>
+        <v>23700</v>
       </c>
       <c r="I35" s="3">
-        <v>30300</v>
+        <v>30700</v>
       </c>
       <c r="J35" s="3">
-        <v>21000</v>
+        <v>21300</v>
       </c>
       <c r="K35" s="3">
         <v>29700</v>
@@ -1821,25 +1821,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>282000</v>
+        <v>286300</v>
       </c>
       <c r="E41" s="3">
-        <v>314700</v>
+        <v>319400</v>
       </c>
       <c r="F41" s="3">
-        <v>282000</v>
+        <v>286200</v>
       </c>
       <c r="G41" s="3">
-        <v>256800</v>
+        <v>260600</v>
       </c>
       <c r="H41" s="3">
-        <v>212200</v>
+        <v>215400</v>
       </c>
       <c r="I41" s="3">
-        <v>283700</v>
+        <v>288000</v>
       </c>
       <c r="J41" s="3">
-        <v>145800</v>
+        <v>148000</v>
       </c>
       <c r="K41" s="3">
         <v>143800</v>
@@ -1860,22 +1860,22 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>12700</v>
+        <v>12900</v>
       </c>
       <c r="E42" s="3">
-        <v>8600</v>
+        <v>8700</v>
       </c>
       <c r="F42" s="3">
-        <v>13100</v>
+        <v>13300</v>
       </c>
       <c r="G42" s="3">
-        <v>17700</v>
+        <v>18000</v>
       </c>
       <c r="H42" s="3">
-        <v>10500</v>
+        <v>10700</v>
       </c>
       <c r="I42" s="3">
-        <v>25000</v>
+        <v>25300</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>10</v>
@@ -1899,25 +1899,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>563500</v>
+        <v>571900</v>
       </c>
       <c r="E43" s="3">
-        <v>262400</v>
+        <v>266400</v>
       </c>
       <c r="F43" s="3">
-        <v>239600</v>
+        <v>243200</v>
       </c>
       <c r="G43" s="3">
-        <v>219000</v>
+        <v>222300</v>
       </c>
       <c r="H43" s="3">
-        <v>221600</v>
+        <v>225000</v>
       </c>
       <c r="I43" s="3">
-        <v>421000</v>
+        <v>427300</v>
       </c>
       <c r="J43" s="3">
-        <v>181700</v>
+        <v>184500</v>
       </c>
       <c r="K43" s="3">
         <v>174400</v>
@@ -1938,25 +1938,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>42300</v>
+        <v>43000</v>
       </c>
       <c r="E44" s="3">
-        <v>17300</v>
+        <v>17600</v>
       </c>
       <c r="F44" s="3">
-        <v>14400</v>
+        <v>14600</v>
       </c>
       <c r="G44" s="3">
-        <v>16400</v>
+        <v>16700</v>
       </c>
       <c r="H44" s="3">
-        <v>22600</v>
+        <v>22900</v>
       </c>
       <c r="I44" s="3">
-        <v>21600</v>
+        <v>22000</v>
       </c>
       <c r="J44" s="3">
-        <v>18600</v>
+        <v>18900</v>
       </c>
       <c r="K44" s="3">
         <v>14700</v>
@@ -1977,25 +1977,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>103500</v>
+        <v>105000</v>
       </c>
       <c r="E45" s="3">
-        <v>90800</v>
+        <v>92200</v>
       </c>
       <c r="F45" s="3">
-        <v>71100</v>
+        <v>72200</v>
       </c>
       <c r="G45" s="3">
-        <v>65000</v>
+        <v>66000</v>
       </c>
       <c r="H45" s="3">
-        <v>57500</v>
+        <v>58300</v>
       </c>
       <c r="I45" s="3">
-        <v>132100</v>
+        <v>134000</v>
       </c>
       <c r="J45" s="3">
-        <v>77000</v>
+        <v>78200</v>
       </c>
       <c r="K45" s="3">
         <v>59600</v>
@@ -2016,25 +2016,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>708300</v>
+        <v>719000</v>
       </c>
       <c r="E46" s="3">
-        <v>693800</v>
+        <v>704200</v>
       </c>
       <c r="F46" s="3">
-        <v>620200</v>
+        <v>629500</v>
       </c>
       <c r="G46" s="3">
-        <v>575000</v>
+        <v>583600</v>
       </c>
       <c r="H46" s="3">
-        <v>524400</v>
+        <v>532300</v>
       </c>
       <c r="I46" s="3">
-        <v>437200</v>
+        <v>443800</v>
       </c>
       <c r="J46" s="3">
-        <v>423100</v>
+        <v>429500</v>
       </c>
       <c r="K46" s="3">
         <v>392500</v>
@@ -2055,25 +2055,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>197100</v>
+        <v>200000</v>
       </c>
       <c r="E47" s="3">
-        <v>183000</v>
+        <v>185700</v>
       </c>
       <c r="F47" s="3">
-        <v>175500</v>
+        <v>178100</v>
       </c>
       <c r="G47" s="3">
-        <v>124300</v>
+        <v>126200</v>
       </c>
       <c r="H47" s="3">
-        <v>143000</v>
+        <v>145100</v>
       </c>
       <c r="I47" s="3">
-        <v>187100</v>
+        <v>189900</v>
       </c>
       <c r="J47" s="3">
-        <v>20500</v>
+        <v>20800</v>
       </c>
       <c r="K47" s="3">
         <v>21400</v>
@@ -2094,25 +2094,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>929500</v>
+        <v>943500</v>
       </c>
       <c r="E48" s="3">
-        <v>416500</v>
+        <v>422700</v>
       </c>
       <c r="F48" s="3">
-        <v>450100</v>
+        <v>456900</v>
       </c>
       <c r="G48" s="3">
-        <v>451300</v>
+        <v>458100</v>
       </c>
       <c r="H48" s="3">
-        <v>220000</v>
+        <v>223300</v>
       </c>
       <c r="I48" s="3">
-        <v>530800</v>
+        <v>538800</v>
       </c>
       <c r="J48" s="3">
-        <v>264100</v>
+        <v>268100</v>
       </c>
       <c r="K48" s="3">
         <v>252300</v>
@@ -2133,25 +2133,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>351600</v>
+        <v>356900</v>
       </c>
       <c r="E49" s="3">
-        <v>172000</v>
+        <v>174600</v>
       </c>
       <c r="F49" s="3">
-        <v>153000</v>
+        <v>155300</v>
       </c>
       <c r="G49" s="3">
-        <v>161800</v>
+        <v>164200</v>
       </c>
       <c r="H49" s="3">
-        <v>165300</v>
+        <v>167800</v>
       </c>
       <c r="I49" s="3">
-        <v>216700</v>
+        <v>219900</v>
       </c>
       <c r="J49" s="3">
-        <v>61500</v>
+        <v>62400</v>
       </c>
       <c r="K49" s="3">
         <v>71400</v>
@@ -2250,25 +2250,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>89600</v>
+        <v>90900</v>
       </c>
       <c r="E52" s="3">
-        <v>74000</v>
+        <v>75100</v>
       </c>
       <c r="F52" s="3">
-        <v>67200</v>
+        <v>68200</v>
       </c>
       <c r="G52" s="3">
+        <v>59900</v>
+      </c>
+      <c r="H52" s="3">
         <v>59000</v>
       </c>
-      <c r="H52" s="3">
-        <v>58100</v>
-      </c>
       <c r="I52" s="3">
-        <v>231300</v>
+        <v>234800</v>
       </c>
       <c r="J52" s="3">
-        <v>143100</v>
+        <v>145300</v>
       </c>
       <c r="K52" s="3">
         <v>128400</v>
@@ -2328,25 +2328,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1635600</v>
+        <v>1660200</v>
       </c>
       <c r="E54" s="3">
-        <v>1539200</v>
+        <v>1562400</v>
       </c>
       <c r="F54" s="3">
-        <v>1466000</v>
+        <v>1488000</v>
       </c>
       <c r="G54" s="3">
-        <v>1371300</v>
+        <v>1392000</v>
       </c>
       <c r="H54" s="3">
-        <v>1110800</v>
+        <v>1127500</v>
       </c>
       <c r="I54" s="3">
-        <v>1030300</v>
+        <v>1045800</v>
       </c>
       <c r="J54" s="3">
-        <v>912300</v>
+        <v>926000</v>
       </c>
       <c r="K54" s="3">
         <v>866100</v>
@@ -2401,25 +2401,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>215800</v>
+        <v>219000</v>
       </c>
       <c r="E57" s="3">
-        <v>57900</v>
+        <v>58800</v>
       </c>
       <c r="F57" s="3">
-        <v>42400</v>
+        <v>43100</v>
       </c>
       <c r="G57" s="3">
-        <v>39700</v>
+        <v>40300</v>
       </c>
       <c r="H57" s="3">
-        <v>51900</v>
+        <v>52600</v>
       </c>
       <c r="I57" s="3">
-        <v>135300</v>
+        <v>137300</v>
       </c>
       <c r="J57" s="3">
-        <v>97300</v>
+        <v>98800</v>
       </c>
       <c r="K57" s="3">
         <v>102200</v>
@@ -2440,25 +2440,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>223500</v>
+        <v>226800</v>
       </c>
       <c r="E58" s="3">
-        <v>108700</v>
+        <v>110300</v>
       </c>
       <c r="F58" s="3">
-        <v>123200</v>
+        <v>125100</v>
       </c>
       <c r="G58" s="3">
-        <v>103500</v>
+        <v>105000</v>
       </c>
       <c r="H58" s="3">
-        <v>127900</v>
+        <v>129900</v>
       </c>
       <c r="I58" s="3">
-        <v>197900</v>
+        <v>200900</v>
       </c>
       <c r="J58" s="3">
-        <v>93400</v>
+        <v>94800</v>
       </c>
       <c r="K58" s="3">
         <v>97100</v>
@@ -2479,25 +2479,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>337600</v>
+        <v>342700</v>
       </c>
       <c r="E59" s="3">
-        <v>343200</v>
+        <v>348400</v>
       </c>
       <c r="F59" s="3">
-        <v>320800</v>
+        <v>325600</v>
       </c>
       <c r="G59" s="3">
-        <v>293000</v>
+        <v>297400</v>
       </c>
       <c r="H59" s="3">
-        <v>171500</v>
+        <v>174100</v>
       </c>
       <c r="I59" s="3">
-        <v>226500</v>
+        <v>229900</v>
       </c>
       <c r="J59" s="3">
-        <v>74800</v>
+        <v>75900</v>
       </c>
       <c r="K59" s="3">
         <v>65800</v>
@@ -2518,25 +2518,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>517000</v>
+        <v>524800</v>
       </c>
       <c r="E60" s="3">
-        <v>509800</v>
+        <v>517500</v>
       </c>
       <c r="F60" s="3">
-        <v>486400</v>
+        <v>493800</v>
       </c>
       <c r="G60" s="3">
-        <v>436200</v>
+        <v>442700</v>
       </c>
       <c r="H60" s="3">
-        <v>351300</v>
+        <v>356600</v>
       </c>
       <c r="I60" s="3">
-        <v>279800</v>
+        <v>284000</v>
       </c>
       <c r="J60" s="3">
-        <v>265500</v>
+        <v>269500</v>
       </c>
       <c r="K60" s="3">
         <v>265100</v>
@@ -2557,25 +2557,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>23900</v>
+        <v>24300</v>
       </c>
       <c r="E61" s="3">
-        <v>36500</v>
+        <v>37100</v>
       </c>
       <c r="F61" s="3">
-        <v>46500</v>
+        <v>47200</v>
       </c>
       <c r="G61" s="3">
-        <v>80800</v>
+        <v>82000</v>
       </c>
       <c r="H61" s="3">
-        <v>169400</v>
+        <v>172000</v>
       </c>
       <c r="I61" s="3">
-        <v>175400</v>
+        <v>178100</v>
       </c>
       <c r="J61" s="3">
-        <v>125400</v>
+        <v>127300</v>
       </c>
       <c r="K61" s="3">
         <v>57200</v>
@@ -2596,25 +2596,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>510700</v>
+        <v>518400</v>
       </c>
       <c r="E62" s="3">
-        <v>298200</v>
+        <v>302700</v>
       </c>
       <c r="F62" s="3">
-        <v>329000</v>
+        <v>333900</v>
       </c>
       <c r="G62" s="3">
-        <v>322800</v>
+        <v>327600</v>
       </c>
       <c r="H62" s="3">
-        <v>78000</v>
+        <v>79200</v>
       </c>
       <c r="I62" s="3">
-        <v>147800</v>
+        <v>150000</v>
       </c>
       <c r="J62" s="3">
-        <v>74000</v>
+        <v>75100</v>
       </c>
       <c r="K62" s="3">
         <v>63500</v>
@@ -2752,25 +2752,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>850400</v>
+        <v>863200</v>
       </c>
       <c r="E66" s="3">
-        <v>851800</v>
+        <v>864600</v>
       </c>
       <c r="F66" s="3">
-        <v>868700</v>
+        <v>881700</v>
       </c>
       <c r="G66" s="3">
-        <v>846300</v>
+        <v>859000</v>
       </c>
       <c r="H66" s="3">
-        <v>604400</v>
+        <v>613500</v>
       </c>
       <c r="I66" s="3">
-        <v>535400</v>
+        <v>543500</v>
       </c>
       <c r="J66" s="3">
-        <v>469100</v>
+        <v>476200</v>
       </c>
       <c r="K66" s="3">
         <v>389500</v>
@@ -2964,25 +2964,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>340000</v>
+        <v>345100</v>
       </c>
       <c r="E72" s="3">
-        <v>245800</v>
+        <v>249500</v>
       </c>
       <c r="F72" s="3">
-        <v>166300</v>
+        <v>168800</v>
       </c>
       <c r="G72" s="3">
-        <v>109600</v>
+        <v>111200</v>
       </c>
       <c r="H72" s="3">
-        <v>81900</v>
+        <v>83100</v>
       </c>
       <c r="I72" s="3">
-        <v>120100</v>
+        <v>121900</v>
       </c>
       <c r="J72" s="3">
-        <v>30000</v>
+        <v>30400</v>
       </c>
       <c r="K72" s="3">
         <v>18200</v>
@@ -3120,25 +3120,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>785100</v>
+        <v>797000</v>
       </c>
       <c r="E76" s="3">
-        <v>687400</v>
+        <v>697800</v>
       </c>
       <c r="F76" s="3">
-        <v>597300</v>
+        <v>606300</v>
       </c>
       <c r="G76" s="3">
-        <v>525100</v>
+        <v>533000</v>
       </c>
       <c r="H76" s="3">
-        <v>506400</v>
+        <v>514100</v>
       </c>
       <c r="I76" s="3">
-        <v>494900</v>
+        <v>502300</v>
       </c>
       <c r="J76" s="3">
-        <v>443200</v>
+        <v>449800</v>
       </c>
       <c r="K76" s="3">
         <v>476600</v>
@@ -3242,25 +3242,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>125100</v>
+        <v>127000</v>
       </c>
       <c r="E81" s="3">
-        <v>104100</v>
+        <v>105600</v>
       </c>
       <c r="F81" s="3">
-        <v>64500</v>
+        <v>65500</v>
       </c>
       <c r="G81" s="3">
-        <v>26600</v>
+        <v>27000</v>
       </c>
       <c r="H81" s="3">
-        <v>23400</v>
+        <v>23700</v>
       </c>
       <c r="I81" s="3">
-        <v>30300</v>
+        <v>30700</v>
       </c>
       <c r="J81" s="3">
-        <v>21000</v>
+        <v>21300</v>
       </c>
       <c r="K81" s="3">
         <v>29700</v>
@@ -3298,25 +3298,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>191200</v>
+        <v>194100</v>
       </c>
       <c r="E83" s="3">
-        <v>188900</v>
+        <v>191700</v>
       </c>
       <c r="F83" s="3">
-        <v>185700</v>
+        <v>188500</v>
       </c>
       <c r="G83" s="3">
-        <v>189400</v>
+        <v>192200</v>
       </c>
       <c r="H83" s="3">
-        <v>103800</v>
+        <v>105300</v>
       </c>
       <c r="I83" s="3">
-        <v>89100</v>
+        <v>90400</v>
       </c>
       <c r="J83" s="3">
-        <v>72300</v>
+        <v>73400</v>
       </c>
       <c r="K83" s="3">
         <v>72900</v>
@@ -3532,25 +3532,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>255800</v>
+        <v>259700</v>
       </c>
       <c r="E89" s="3">
-        <v>289300</v>
+        <v>293700</v>
       </c>
       <c r="F89" s="3">
-        <v>269200</v>
+        <v>273300</v>
       </c>
       <c r="G89" s="3">
-        <v>221700</v>
+        <v>225100</v>
       </c>
       <c r="H89" s="3">
-        <v>167000</v>
+        <v>169500</v>
       </c>
       <c r="I89" s="3">
-        <v>97400</v>
+        <v>98800</v>
       </c>
       <c r="J89" s="3">
-        <v>48900</v>
+        <v>49700</v>
       </c>
       <c r="K89" s="3">
         <v>88600</v>
@@ -3588,25 +3588,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-78300</v>
+        <v>-79400</v>
       </c>
       <c r="E91" s="3">
-        <v>-45000</v>
+        <v>-45700</v>
       </c>
       <c r="F91" s="3">
-        <v>-42400</v>
+        <v>-43100</v>
       </c>
       <c r="G91" s="3">
-        <v>-47800</v>
+        <v>-48500</v>
       </c>
       <c r="H91" s="3">
-        <v>-47000</v>
+        <v>-47700</v>
       </c>
       <c r="I91" s="3">
-        <v>-178400</v>
+        <v>-181100</v>
       </c>
       <c r="J91" s="3">
-        <v>-70500</v>
+        <v>-71600</v>
       </c>
       <c r="K91" s="3">
         <v>-80100</v>
@@ -3705,25 +3705,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-122100</v>
+        <v>-123900</v>
       </c>
       <c r="E94" s="3">
-        <v>-78600</v>
+        <v>-79800</v>
       </c>
       <c r="F94" s="3">
-        <v>-87800</v>
+        <v>-89100</v>
       </c>
       <c r="G94" s="3">
-        <v>-48200</v>
+        <v>-49000</v>
       </c>
       <c r="H94" s="3">
-        <v>-57700</v>
+        <v>-58600</v>
       </c>
       <c r="I94" s="3">
-        <v>-94900</v>
+        <v>-96400</v>
       </c>
       <c r="J94" s="3">
-        <v>-49000</v>
+        <v>-49700</v>
       </c>
       <c r="K94" s="3">
         <v>-61600</v>
@@ -3761,25 +3761,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-32500</v>
+        <v>-33000</v>
       </c>
       <c r="E96" s="3">
-        <v>-25500</v>
+        <v>-25900</v>
       </c>
       <c r="F96" s="3">
-        <v>-10200</v>
+        <v>-10300</v>
       </c>
       <c r="G96" s="3">
-        <v>-8100</v>
+        <v>-8200</v>
       </c>
       <c r="H96" s="3">
-        <v>-8100</v>
+        <v>-8200</v>
       </c>
       <c r="I96" s="3">
-        <v>-8100</v>
+        <v>-8200</v>
       </c>
       <c r="J96" s="3">
-        <v>-7500</v>
+        <v>-7600</v>
       </c>
       <c r="K96" s="3">
         <v>-7400</v>
@@ -3917,25 +3917,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-170900</v>
+        <v>-173400</v>
       </c>
       <c r="E100" s="3">
-        <v>-181200</v>
+        <v>-184000</v>
       </c>
       <c r="F100" s="3">
-        <v>-156800</v>
+        <v>-159200</v>
       </c>
       <c r="G100" s="3">
-        <v>-128500</v>
+        <v>-130400</v>
       </c>
       <c r="H100" s="3">
-        <v>-39100</v>
+        <v>-39700</v>
       </c>
       <c r="I100" s="3">
         <v>-4800</v>
       </c>
       <c r="J100" s="3">
-        <v>16500</v>
+        <v>16800</v>
       </c>
       <c r="K100" s="3">
         <v>-38200</v>
@@ -3956,10 +3956,10 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="E101" s="3">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="F101" s="3">
         <v>600</v>
@@ -3995,25 +3995,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-32700</v>
+        <v>-33200</v>
       </c>
       <c r="E102" s="3">
-        <v>32700</v>
+        <v>33200</v>
       </c>
       <c r="F102" s="3">
-        <v>25200</v>
+        <v>25600</v>
       </c>
       <c r="G102" s="3">
-        <v>44600</v>
+        <v>45300</v>
       </c>
       <c r="H102" s="3">
-        <v>70600</v>
+        <v>71700</v>
       </c>
       <c r="I102" s="3">
-        <v>-2800</v>
+        <v>-2900</v>
       </c>
       <c r="J102" s="3">
-        <v>15900</v>
+        <v>16100</v>
       </c>
       <c r="K102" s="3">
         <v>-11200</v>

--- a/AAII_Financials/Yearly/IIJIY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IIJIY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
   <si>
     <t>IIJIY</t>
   </si>
@@ -656,183 +656,195 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44651</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44286</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43921</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43555</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43190</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42825</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42460</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42094</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41729</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41364</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1703300</v>
+        <v>1761400</v>
       </c>
       <c r="E8" s="3">
-        <v>1525500</v>
+        <v>1612300</v>
       </c>
       <c r="F8" s="3">
-        <v>1435600</v>
+        <v>1444000</v>
       </c>
       <c r="G8" s="3">
-        <v>1378200</v>
+        <v>1359000</v>
       </c>
       <c r="H8" s="3">
-        <v>1297000</v>
+        <v>1304500</v>
       </c>
       <c r="I8" s="3">
-        <v>1187800</v>
+        <v>1227700</v>
       </c>
       <c r="J8" s="3">
+        <v>1124400</v>
+      </c>
+      <c r="K8" s="3">
         <v>1063500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1033800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1049600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1046700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>965800</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1313000</v>
+        <v>1353900</v>
       </c>
       <c r="E9" s="3">
-        <v>1177500</v>
+        <v>1885800</v>
       </c>
       <c r="F9" s="3">
-        <v>1164100</v>
+        <v>1114600</v>
       </c>
       <c r="G9" s="3">
-        <v>1158500</v>
+        <v>1102000</v>
       </c>
       <c r="H9" s="3">
-        <v>1101700</v>
+        <v>1096600</v>
       </c>
       <c r="I9" s="3">
-        <v>1977000</v>
+        <v>1042800</v>
       </c>
       <c r="J9" s="3">
+        <v>1871400</v>
+      </c>
+      <c r="K9" s="3">
         <v>893300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>852500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>861300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>853800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>767100</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>390300</v>
+        <v>407500</v>
       </c>
       <c r="E10" s="3">
-        <v>348000</v>
+        <v>-273500</v>
       </c>
       <c r="F10" s="3">
-        <v>271500</v>
+        <v>329400</v>
       </c>
       <c r="G10" s="3">
-        <v>219700</v>
+        <v>257000</v>
       </c>
       <c r="H10" s="3">
-        <v>195300</v>
+        <v>207900</v>
       </c>
       <c r="I10" s="3">
-        <v>-789100</v>
+        <v>184900</v>
       </c>
       <c r="J10" s="3">
+        <v>-747000</v>
+      </c>
+      <c r="K10" s="3">
         <v>170200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>181200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>188300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>193000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>198600</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,16 +860,17 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>3700</v>
+      <c r="D12" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E12" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="F12" s="3">
         <v>3200</v>
@@ -866,29 +879,32 @@
         <v>3000</v>
       </c>
       <c r="H12" s="3">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="I12" s="3">
-        <v>3300</v>
+        <v>2800</v>
       </c>
       <c r="J12" s="3">
         <v>3100</v>
       </c>
       <c r="K12" s="3">
+        <v>3100</v>
+      </c>
+      <c r="L12" s="3">
         <v>3300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3700</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -925,71 +941,77 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F14" s="3">
+        <v>8900</v>
+      </c>
+      <c r="G14" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I14" s="3">
         <v>2000</v>
       </c>
-      <c r="E14" s="3">
-        <v>9400</v>
-      </c>
-      <c r="F14" s="3">
-        <v>2700</v>
-      </c>
-      <c r="G14" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H14" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I14" s="3">
-        <v>1500</v>
-      </c>
       <c r="J14" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>200</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>20800</v>
+      <c r="D15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E15" s="3">
-        <v>21100</v>
+        <v>19600</v>
       </c>
       <c r="F15" s="3">
-        <v>19100</v>
+        <v>19900</v>
       </c>
       <c r="G15" s="3">
-        <v>19100</v>
+        <v>18100</v>
       </c>
       <c r="H15" s="3">
-        <v>8600</v>
+        <v>18100</v>
       </c>
       <c r="I15" s="3">
-        <v>8400</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>10</v>
+        <v>8200</v>
+      </c>
+      <c r="J15" s="3">
+        <v>8000</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>10</v>
@@ -1003,9 +1025,12 @@
       <c r="N15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1018,86 +1043,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1519800</v>
+        <v>1576200</v>
       </c>
       <c r="E17" s="3">
-        <v>1374800</v>
+        <v>1438600</v>
       </c>
       <c r="F17" s="3">
-        <v>1337300</v>
+        <v>1301300</v>
       </c>
       <c r="G17" s="3">
-        <v>1320200</v>
+        <v>1265800</v>
       </c>
       <c r="H17" s="3">
-        <v>1256400</v>
+        <v>1249700</v>
       </c>
       <c r="I17" s="3">
-        <v>1142200</v>
+        <v>1189300</v>
       </c>
       <c r="J17" s="3">
+        <v>1081200</v>
+      </c>
+      <c r="K17" s="3">
         <v>1029100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>988700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1006600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>994300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>895500</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>183500</v>
+        <v>185200</v>
       </c>
       <c r="E18" s="3">
-        <v>150700</v>
+        <v>173700</v>
       </c>
       <c r="F18" s="3">
-        <v>98400</v>
+        <v>142700</v>
       </c>
       <c r="G18" s="3">
-        <v>58000</v>
+        <v>93100</v>
       </c>
       <c r="H18" s="3">
-        <v>40600</v>
+        <v>54900</v>
       </c>
       <c r="I18" s="3">
-        <v>45600</v>
+        <v>38400</v>
       </c>
       <c r="J18" s="3">
+        <v>43200</v>
+      </c>
+      <c r="K18" s="3">
         <v>34400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>45000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>43000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>52400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>70300</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1113,203 +1145,219 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>3900</v>
+        <v>-600</v>
       </c>
       <c r="E20" s="3">
-        <v>15600</v>
+        <v>3700</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>14700</v>
       </c>
       <c r="G20" s="3">
-        <v>-5900</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>1700</v>
+        <v>-5600</v>
       </c>
       <c r="I20" s="3">
-        <v>6000</v>
+        <v>1600</v>
       </c>
       <c r="J20" s="3">
+        <v>5600</v>
+      </c>
+      <c r="K20" s="3">
         <v>4200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2800</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>382400</v>
+        <v>371200</v>
       </c>
       <c r="E21" s="3">
-        <v>358900</v>
+        <v>360900</v>
       </c>
       <c r="F21" s="3">
-        <v>287700</v>
+        <v>338600</v>
       </c>
       <c r="G21" s="3">
-        <v>245100</v>
+        <v>271300</v>
       </c>
       <c r="H21" s="3">
-        <v>148100</v>
+        <v>231000</v>
       </c>
       <c r="I21" s="3">
-        <v>142400</v>
+        <v>139600</v>
       </c>
       <c r="J21" s="3">
+        <v>134300</v>
+      </c>
+      <c r="K21" s="3">
         <v>112400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>119500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>129400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>141000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>141500</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F22" s="3">
         <v>3300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>3500</v>
       </c>
-      <c r="F22" s="3">
-        <v>3700</v>
-      </c>
-      <c r="G22" s="3">
-        <v>3800</v>
-      </c>
       <c r="H22" s="3">
-        <v>2900</v>
+        <v>3600</v>
       </c>
       <c r="I22" s="3">
-        <v>5300</v>
+        <v>2700</v>
       </c>
       <c r="J22" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K22" s="3">
         <v>2000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2600</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>184100</v>
+        <v>184600</v>
       </c>
       <c r="E23" s="3">
-        <v>162900</v>
+        <v>174200</v>
       </c>
       <c r="F23" s="3">
-        <v>94600</v>
+        <v>154200</v>
       </c>
       <c r="G23" s="3">
-        <v>48300</v>
+        <v>89500</v>
       </c>
       <c r="H23" s="3">
-        <v>39400</v>
+        <v>45700</v>
       </c>
       <c r="I23" s="3">
-        <v>46300</v>
+        <v>37300</v>
       </c>
       <c r="J23" s="3">
+        <v>43800</v>
+      </c>
+      <c r="K23" s="3">
         <v>36600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>45500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>43800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>57500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>70500</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>56100</v>
+        <v>57200</v>
       </c>
       <c r="E24" s="3">
-        <v>56400</v>
+        <v>53100</v>
       </c>
       <c r="F24" s="3">
-        <v>28500</v>
+        <v>53300</v>
       </c>
       <c r="G24" s="3">
-        <v>20000</v>
+        <v>27000</v>
       </c>
       <c r="H24" s="3">
-        <v>14500</v>
+        <v>18900</v>
       </c>
       <c r="I24" s="3">
-        <v>15500</v>
+        <v>13700</v>
       </c>
       <c r="J24" s="3">
+        <v>14700</v>
+      </c>
+      <c r="K24" s="3">
         <v>15000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>16000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>16200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>16400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>23700</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1346,87 +1394,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>127900</v>
+        <v>127400</v>
       </c>
       <c r="E26" s="3">
-        <v>106500</v>
+        <v>121200</v>
       </c>
       <c r="F26" s="3">
-        <v>66100</v>
+        <v>100800</v>
       </c>
       <c r="G26" s="3">
-        <v>28300</v>
+        <v>62500</v>
       </c>
       <c r="H26" s="3">
-        <v>24900</v>
+        <v>26800</v>
       </c>
       <c r="I26" s="3">
-        <v>30800</v>
+        <v>23600</v>
       </c>
       <c r="J26" s="3">
+        <v>29200</v>
+      </c>
+      <c r="K26" s="3">
         <v>21600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>29500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>27700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>41000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>46800</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>127000</v>
+        <v>126500</v>
       </c>
       <c r="E27" s="3">
-        <v>105600</v>
+        <v>120300</v>
       </c>
       <c r="F27" s="3">
-        <v>65500</v>
+        <v>100000</v>
       </c>
       <c r="G27" s="3">
-        <v>27000</v>
+        <v>62000</v>
       </c>
       <c r="H27" s="3">
-        <v>23700</v>
+        <v>25600</v>
       </c>
       <c r="I27" s="3">
-        <v>30600</v>
+        <v>22500</v>
       </c>
       <c r="J27" s="3">
+        <v>29000</v>
+      </c>
+      <c r="K27" s="3">
         <v>21300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>29700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>28300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>41000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>48200</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1463,9 +1520,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1484,11 +1544,11 @@
       <c r="H29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J29" s="3">
         <v>100</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>10</v>
@@ -1502,9 +1562,12 @@
       <c r="N29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1541,9 +1604,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1580,87 +1646,96 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-3900</v>
+        <v>600</v>
       </c>
       <c r="E32" s="3">
-        <v>-15600</v>
+        <v>-3700</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-14700</v>
       </c>
       <c r="G32" s="3">
-        <v>5900</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-1700</v>
+        <v>5600</v>
       </c>
       <c r="I32" s="3">
-        <v>-6000</v>
+        <v>-1600</v>
       </c>
       <c r="J32" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="K32" s="3">
         <v>-4200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2800</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>127000</v>
+        <v>126500</v>
       </c>
       <c r="E33" s="3">
-        <v>105600</v>
+        <v>120300</v>
       </c>
       <c r="F33" s="3">
-        <v>65500</v>
+        <v>100000</v>
       </c>
       <c r="G33" s="3">
-        <v>27000</v>
+        <v>62000</v>
       </c>
       <c r="H33" s="3">
-        <v>23700</v>
+        <v>25600</v>
       </c>
       <c r="I33" s="3">
-        <v>30700</v>
+        <v>22500</v>
       </c>
       <c r="J33" s="3">
+        <v>29100</v>
+      </c>
+      <c r="K33" s="3">
         <v>21300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>29700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>28300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>41000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>48200</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1697,92 +1772,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>127000</v>
+        <v>126500</v>
       </c>
       <c r="E35" s="3">
-        <v>105600</v>
+        <v>120300</v>
       </c>
       <c r="F35" s="3">
-        <v>65500</v>
+        <v>100000</v>
       </c>
       <c r="G35" s="3">
-        <v>27000</v>
+        <v>62000</v>
       </c>
       <c r="H35" s="3">
-        <v>23700</v>
+        <v>25600</v>
       </c>
       <c r="I35" s="3">
-        <v>30700</v>
+        <v>22500</v>
       </c>
       <c r="J35" s="3">
+        <v>29100</v>
+      </c>
+      <c r="K35" s="3">
         <v>21300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>29700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>28300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>41000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>48200</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44651</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44286</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43921</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43555</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43190</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42825</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42460</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42094</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41729</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41364</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1798,8 +1882,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1815,70 +1900,74 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>286300</v>
+        <v>290100</v>
       </c>
       <c r="E41" s="3">
-        <v>319400</v>
+        <v>271000</v>
       </c>
       <c r="F41" s="3">
-        <v>286200</v>
+        <v>302400</v>
       </c>
       <c r="G41" s="3">
-        <v>260600</v>
+        <v>270900</v>
       </c>
       <c r="H41" s="3">
-        <v>215400</v>
+        <v>246700</v>
       </c>
       <c r="I41" s="3">
-        <v>288000</v>
+        <v>203900</v>
       </c>
       <c r="J41" s="3">
+        <v>272600</v>
+      </c>
+      <c r="K41" s="3">
         <v>148000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>143800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>179900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>205400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>111400</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>12900</v>
+        <v>9800</v>
       </c>
       <c r="E42" s="3">
-        <v>8700</v>
+        <v>12200</v>
       </c>
       <c r="F42" s="3">
-        <v>13300</v>
+        <v>8300</v>
       </c>
       <c r="G42" s="3">
-        <v>18000</v>
+        <v>12600</v>
       </c>
       <c r="H42" s="3">
-        <v>10700</v>
+        <v>17000</v>
       </c>
       <c r="I42" s="3">
-        <v>25300</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>10</v>
+        <v>10100</v>
+      </c>
+      <c r="J42" s="3">
+        <v>24000</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>10</v>
@@ -1892,282 +1981,306 @@
       <c r="N42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>571900</v>
+        <v>311300</v>
       </c>
       <c r="E43" s="3">
-        <v>266400</v>
+        <v>541400</v>
       </c>
       <c r="F43" s="3">
-        <v>243200</v>
+        <v>252100</v>
       </c>
       <c r="G43" s="3">
-        <v>222300</v>
+        <v>230200</v>
       </c>
       <c r="H43" s="3">
-        <v>225000</v>
+        <v>210400</v>
       </c>
       <c r="I43" s="3">
-        <v>427300</v>
+        <v>212900</v>
       </c>
       <c r="J43" s="3">
+        <v>404500</v>
+      </c>
+      <c r="K43" s="3">
         <v>184500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>174400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>189800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>176000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>170500</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>43000</v>
+        <v>20600</v>
       </c>
       <c r="E44" s="3">
-        <v>17600</v>
+        <v>40700</v>
       </c>
       <c r="F44" s="3">
-        <v>14600</v>
+        <v>16600</v>
       </c>
       <c r="G44" s="3">
-        <v>16700</v>
+        <v>13900</v>
       </c>
       <c r="H44" s="3">
-        <v>22900</v>
+        <v>15800</v>
       </c>
       <c r="I44" s="3">
-        <v>22000</v>
+        <v>21700</v>
       </c>
       <c r="J44" s="3">
+        <v>20800</v>
+      </c>
+      <c r="K44" s="3">
         <v>18900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>14700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>10500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>15300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>11800</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>105000</v>
+        <v>133100</v>
       </c>
       <c r="E45" s="3">
-        <v>92200</v>
+        <v>99400</v>
       </c>
       <c r="F45" s="3">
-        <v>72200</v>
+        <v>87200</v>
       </c>
       <c r="G45" s="3">
-        <v>66000</v>
+        <v>68300</v>
       </c>
       <c r="H45" s="3">
-        <v>58300</v>
+        <v>62500</v>
       </c>
       <c r="I45" s="3">
-        <v>134000</v>
+        <v>55200</v>
       </c>
       <c r="J45" s="3">
+        <v>126900</v>
+      </c>
+      <c r="K45" s="3">
         <v>78200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>59600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>64100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>76900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>46600</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>719000</v>
+        <v>764900</v>
       </c>
       <c r="E46" s="3">
-        <v>704200</v>
+        <v>680600</v>
       </c>
       <c r="F46" s="3">
-        <v>629500</v>
+        <v>666600</v>
       </c>
       <c r="G46" s="3">
-        <v>583600</v>
+        <v>595900</v>
       </c>
       <c r="H46" s="3">
-        <v>532300</v>
+        <v>552400</v>
       </c>
       <c r="I46" s="3">
-        <v>443800</v>
+        <v>503800</v>
       </c>
       <c r="J46" s="3">
+        <v>420100</v>
+      </c>
+      <c r="K46" s="3">
         <v>429500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>392500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>444300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>473600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>340300</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>200000</v>
+        <v>222400</v>
       </c>
       <c r="E47" s="3">
-        <v>185700</v>
+        <v>189300</v>
       </c>
       <c r="F47" s="3">
-        <v>178100</v>
+        <v>175800</v>
       </c>
       <c r="G47" s="3">
-        <v>126200</v>
+        <v>168600</v>
       </c>
       <c r="H47" s="3">
-        <v>145100</v>
+        <v>119400</v>
       </c>
       <c r="I47" s="3">
-        <v>189900</v>
+        <v>137400</v>
       </c>
       <c r="J47" s="3">
+        <v>179700</v>
+      </c>
+      <c r="K47" s="3">
         <v>20800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>21400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>21000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>18500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>14600</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>943500</v>
+        <v>448600</v>
       </c>
       <c r="E48" s="3">
-        <v>422700</v>
+        <v>893100</v>
       </c>
       <c r="F48" s="3">
-        <v>456900</v>
+        <v>400200</v>
       </c>
       <c r="G48" s="3">
-        <v>458100</v>
+        <v>432500</v>
       </c>
       <c r="H48" s="3">
-        <v>223300</v>
+        <v>433600</v>
       </c>
       <c r="I48" s="3">
-        <v>538800</v>
+        <v>211400</v>
       </c>
       <c r="J48" s="3">
+        <v>510000</v>
+      </c>
+      <c r="K48" s="3">
         <v>268100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>252300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>250500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>247100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>209300</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>356900</v>
+        <v>183000</v>
       </c>
       <c r="E49" s="3">
-        <v>174600</v>
+        <v>337800</v>
       </c>
       <c r="F49" s="3">
-        <v>155300</v>
+        <v>165300</v>
       </c>
       <c r="G49" s="3">
-        <v>164200</v>
+        <v>147000</v>
       </c>
       <c r="H49" s="3">
-        <v>167800</v>
+        <v>155400</v>
       </c>
       <c r="I49" s="3">
-        <v>219900</v>
+        <v>158900</v>
       </c>
       <c r="J49" s="3">
+        <v>208200</v>
+      </c>
+      <c r="K49" s="3">
         <v>62400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>71400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>86200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>94400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>97800</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2204,9 +2317,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2243,48 +2359,54 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>90900</v>
+        <v>127400</v>
       </c>
       <c r="E52" s="3">
-        <v>75100</v>
+        <v>86100</v>
       </c>
       <c r="F52" s="3">
-        <v>68200</v>
+        <v>71100</v>
       </c>
       <c r="G52" s="3">
-        <v>59900</v>
+        <v>64500</v>
       </c>
       <c r="H52" s="3">
-        <v>59000</v>
+        <v>56700</v>
       </c>
       <c r="I52" s="3">
-        <v>234800</v>
+        <v>55800</v>
       </c>
       <c r="J52" s="3">
+        <v>222300</v>
+      </c>
+      <c r="K52" s="3">
         <v>145300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>128400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>125100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>117800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>84300</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2321,48 +2443,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1660200</v>
+        <v>1746300</v>
       </c>
       <c r="E54" s="3">
-        <v>1562400</v>
+        <v>1571500</v>
       </c>
       <c r="F54" s="3">
-        <v>1488000</v>
+        <v>1478900</v>
       </c>
       <c r="G54" s="3">
-        <v>1392000</v>
+        <v>1408600</v>
       </c>
       <c r="H54" s="3">
-        <v>1127500</v>
+        <v>1317600</v>
       </c>
       <c r="I54" s="3">
-        <v>1045800</v>
+        <v>1067300</v>
       </c>
       <c r="J54" s="3">
+        <v>989900</v>
+      </c>
+      <c r="K54" s="3">
         <v>926000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>866100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>927300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>951400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>746400</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2378,8 +2506,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2395,242 +2524,261 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>219000</v>
+        <v>162300</v>
       </c>
       <c r="E57" s="3">
-        <v>58800</v>
+        <v>207300</v>
       </c>
       <c r="F57" s="3">
-        <v>43100</v>
+        <v>55700</v>
       </c>
       <c r="G57" s="3">
-        <v>40300</v>
+        <v>40800</v>
       </c>
       <c r="H57" s="3">
-        <v>52600</v>
+        <v>38100</v>
       </c>
       <c r="I57" s="3">
-        <v>137300</v>
+        <v>49800</v>
       </c>
       <c r="J57" s="3">
+        <v>130000</v>
+      </c>
+      <c r="K57" s="3">
         <v>98800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>102200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>103900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>105300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>99700</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>226800</v>
+        <v>192200</v>
       </c>
       <c r="E58" s="3">
-        <v>110300</v>
+        <v>214700</v>
       </c>
       <c r="F58" s="3">
-        <v>125100</v>
+        <v>104400</v>
       </c>
       <c r="G58" s="3">
-        <v>105000</v>
+        <v>118400</v>
       </c>
       <c r="H58" s="3">
-        <v>129900</v>
+        <v>99400</v>
       </c>
       <c r="I58" s="3">
-        <v>200900</v>
+        <v>122900</v>
       </c>
       <c r="J58" s="3">
+        <v>190100</v>
+      </c>
+      <c r="K58" s="3">
         <v>94800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>97100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>108900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>129500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>126500</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>342700</v>
+        <v>273000</v>
       </c>
       <c r="E59" s="3">
-        <v>348400</v>
+        <v>324400</v>
       </c>
       <c r="F59" s="3">
-        <v>325600</v>
+        <v>329700</v>
       </c>
       <c r="G59" s="3">
-        <v>297400</v>
+        <v>308200</v>
       </c>
       <c r="H59" s="3">
-        <v>174100</v>
+        <v>281500</v>
       </c>
       <c r="I59" s="3">
-        <v>229900</v>
+        <v>164800</v>
       </c>
       <c r="J59" s="3">
+        <v>217600</v>
+      </c>
+      <c r="K59" s="3">
         <v>75900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>65800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>74900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>62700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>68100</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>524800</v>
+        <v>627500</v>
       </c>
       <c r="E60" s="3">
-        <v>517500</v>
+        <v>496800</v>
       </c>
       <c r="F60" s="3">
-        <v>493800</v>
+        <v>489800</v>
       </c>
       <c r="G60" s="3">
-        <v>442700</v>
+        <v>467400</v>
       </c>
       <c r="H60" s="3">
-        <v>356600</v>
+        <v>419100</v>
       </c>
       <c r="I60" s="3">
-        <v>284000</v>
+        <v>337500</v>
       </c>
       <c r="J60" s="3">
+        <v>268800</v>
+      </c>
+      <c r="K60" s="3">
         <v>269500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>265100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>287800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>297400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>294400</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>24300</v>
+        <v>300</v>
       </c>
       <c r="E61" s="3">
-        <v>37100</v>
+        <v>23000</v>
       </c>
       <c r="F61" s="3">
-        <v>47200</v>
+        <v>35100</v>
       </c>
       <c r="G61" s="3">
-        <v>82000</v>
+        <v>44700</v>
       </c>
       <c r="H61" s="3">
-        <v>172000</v>
+        <v>77600</v>
       </c>
       <c r="I61" s="3">
-        <v>178100</v>
+        <v>162800</v>
       </c>
       <c r="J61" s="3">
+        <v>168600</v>
+      </c>
+      <c r="K61" s="3">
         <v>127300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>57200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>37000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>42200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>57700</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>518400</v>
+        <v>308000</v>
       </c>
       <c r="E62" s="3">
-        <v>302700</v>
+        <v>490700</v>
       </c>
       <c r="F62" s="3">
-        <v>333900</v>
+        <v>286500</v>
       </c>
       <c r="G62" s="3">
-        <v>327600</v>
+        <v>316100</v>
       </c>
       <c r="H62" s="3">
-        <v>79200</v>
+        <v>310100</v>
       </c>
       <c r="I62" s="3">
-        <v>150000</v>
+        <v>75000</v>
       </c>
       <c r="J62" s="3">
+        <v>142000</v>
+      </c>
+      <c r="K62" s="3">
         <v>75100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>63500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>66400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>60600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>52200</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2667,9 +2815,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2706,9 +2857,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2745,48 +2899,54 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>863200</v>
+        <v>944000</v>
       </c>
       <c r="E66" s="3">
-        <v>864600</v>
+        <v>817100</v>
       </c>
       <c r="F66" s="3">
-        <v>881700</v>
+        <v>818400</v>
       </c>
       <c r="G66" s="3">
-        <v>859000</v>
+        <v>834600</v>
       </c>
       <c r="H66" s="3">
-        <v>613500</v>
+        <v>813100</v>
       </c>
       <c r="I66" s="3">
-        <v>543500</v>
+        <v>580700</v>
       </c>
       <c r="J66" s="3">
+        <v>514400</v>
+      </c>
+      <c r="K66" s="3">
         <v>476200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>389500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>394100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>402600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>404500</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2802,8 +2962,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2840,9 +3001,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2879,9 +3043,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2918,9 +3085,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2957,48 +3127,54 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>345100</v>
+        <v>418600</v>
       </c>
       <c r="E72" s="3">
-        <v>249500</v>
+        <v>326700</v>
       </c>
       <c r="F72" s="3">
-        <v>168800</v>
+        <v>236200</v>
       </c>
       <c r="G72" s="3">
-        <v>111200</v>
+        <v>159800</v>
       </c>
       <c r="H72" s="3">
-        <v>83100</v>
+        <v>105300</v>
       </c>
       <c r="I72" s="3">
-        <v>121900</v>
+        <v>78700</v>
       </c>
       <c r="J72" s="3">
+        <v>115400</v>
+      </c>
+      <c r="K72" s="3">
         <v>30400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-4700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-26300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-58200</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3035,9 +3211,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3074,9 +3253,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3113,48 +3295,54 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>797000</v>
+        <v>802300</v>
       </c>
       <c r="E76" s="3">
-        <v>697800</v>
+        <v>754400</v>
       </c>
       <c r="F76" s="3">
-        <v>606300</v>
+        <v>660500</v>
       </c>
       <c r="G76" s="3">
-        <v>533000</v>
+        <v>573900</v>
       </c>
       <c r="H76" s="3">
-        <v>514100</v>
+        <v>504500</v>
       </c>
       <c r="I76" s="3">
-        <v>502300</v>
+        <v>486600</v>
       </c>
       <c r="J76" s="3">
+        <v>475500</v>
+      </c>
+      <c r="K76" s="3">
         <v>449800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>476600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>533200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>548800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>341800</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3191,92 +3379,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44651</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44286</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43921</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43555</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43190</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42825</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42460</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42094</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41729</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41364</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>127000</v>
+        <v>126500</v>
       </c>
       <c r="E81" s="3">
-        <v>105600</v>
+        <v>120300</v>
       </c>
       <c r="F81" s="3">
-        <v>65500</v>
+        <v>100000</v>
       </c>
       <c r="G81" s="3">
-        <v>27000</v>
+        <v>62000</v>
       </c>
       <c r="H81" s="3">
-        <v>23700</v>
+        <v>25600</v>
       </c>
       <c r="I81" s="3">
-        <v>30700</v>
+        <v>22500</v>
       </c>
       <c r="J81" s="3">
+        <v>29100</v>
+      </c>
+      <c r="K81" s="3">
         <v>21300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>29700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>28300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>41000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>48200</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3292,47 +3489,51 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>194100</v>
+        <v>186900</v>
       </c>
       <c r="E83" s="3">
-        <v>191700</v>
+        <v>183800</v>
       </c>
       <c r="F83" s="3">
-        <v>188500</v>
+        <v>181500</v>
       </c>
       <c r="G83" s="3">
-        <v>192200</v>
+        <v>178500</v>
       </c>
       <c r="H83" s="3">
-        <v>105300</v>
+        <v>182000</v>
       </c>
       <c r="I83" s="3">
-        <v>90400</v>
+        <v>99700</v>
       </c>
       <c r="J83" s="3">
+        <v>85600</v>
+      </c>
+      <c r="K83" s="3">
         <v>73400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>72900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>82500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>80800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>68200</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3369,9 +3570,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3408,9 +3612,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3447,9 +3654,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3486,9 +3696,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3525,48 +3738,54 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>259700</v>
+        <v>260200</v>
       </c>
       <c r="E89" s="3">
-        <v>293700</v>
+        <v>245800</v>
       </c>
       <c r="F89" s="3">
-        <v>273300</v>
+        <v>278000</v>
       </c>
       <c r="G89" s="3">
-        <v>225100</v>
+        <v>258700</v>
       </c>
       <c r="H89" s="3">
-        <v>169500</v>
+        <v>213100</v>
       </c>
       <c r="I89" s="3">
-        <v>98800</v>
+        <v>160500</v>
       </c>
       <c r="J89" s="3">
+        <v>93600</v>
+      </c>
+      <c r="K89" s="3">
         <v>49700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>88600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>110100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>80500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>88700</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3582,47 +3801,51 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-79400</v>
+        <v>-74900</v>
       </c>
       <c r="E91" s="3">
-        <v>-45700</v>
+        <v>-75200</v>
       </c>
       <c r="F91" s="3">
-        <v>-43100</v>
+        <v>-43300</v>
       </c>
       <c r="G91" s="3">
-        <v>-48500</v>
+        <v>-40800</v>
       </c>
       <c r="H91" s="3">
-        <v>-47700</v>
+        <v>-45900</v>
       </c>
       <c r="I91" s="3">
-        <v>-181100</v>
+        <v>-45200</v>
       </c>
       <c r="J91" s="3">
+        <v>-171400</v>
+      </c>
+      <c r="K91" s="3">
         <v>-71600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-80100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-69600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-83600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-50800</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3659,9 +3882,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3698,48 +3924,54 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-123900</v>
+        <v>-114400</v>
       </c>
       <c r="E94" s="3">
-        <v>-79800</v>
+        <v>-117300</v>
       </c>
       <c r="F94" s="3">
-        <v>-89100</v>
+        <v>-75500</v>
       </c>
       <c r="G94" s="3">
-        <v>-49000</v>
+        <v>-84300</v>
       </c>
       <c r="H94" s="3">
-        <v>-58600</v>
+        <v>-46300</v>
       </c>
       <c r="I94" s="3">
-        <v>-96400</v>
+        <v>-55400</v>
       </c>
       <c r="J94" s="3">
+        <v>-91200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-49700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-61600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-68900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-93500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-54000</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3755,47 +3987,51 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-33000</v>
+        <v>-36300</v>
       </c>
       <c r="E96" s="3">
-        <v>-25900</v>
+        <v>-31300</v>
       </c>
       <c r="F96" s="3">
-        <v>-10300</v>
+        <v>-24500</v>
       </c>
       <c r="G96" s="3">
-        <v>-8200</v>
+        <v>-9800</v>
       </c>
       <c r="H96" s="3">
-        <v>-8200</v>
+        <v>-7800</v>
       </c>
       <c r="I96" s="3">
-        <v>-8200</v>
+        <v>-7800</v>
       </c>
       <c r="J96" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="K96" s="3">
         <v>-7600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-7400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-8600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-8300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-6400</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3832,9 +4068,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3871,9 +4110,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3910,124 +4152,136 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-173400</v>
+        <v>-132700</v>
       </c>
       <c r="E100" s="3">
-        <v>-184000</v>
+        <v>-164200</v>
       </c>
       <c r="F100" s="3">
-        <v>-159200</v>
+        <v>-174100</v>
       </c>
       <c r="G100" s="3">
-        <v>-130400</v>
+        <v>-150700</v>
       </c>
       <c r="H100" s="3">
-        <v>-39700</v>
+        <v>-123500</v>
       </c>
       <c r="I100" s="3">
-        <v>-4800</v>
+        <v>-37600</v>
       </c>
       <c r="J100" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="K100" s="3">
         <v>16800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-38200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-53600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>104300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-45400</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="E101" s="3">
-        <v>3300</v>
+        <v>4300</v>
       </c>
       <c r="F101" s="3">
-        <v>600</v>
+        <v>3100</v>
       </c>
       <c r="G101" s="3">
+        <v>500</v>
+      </c>
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-600</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-800</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-33200</v>
+        <v>19200</v>
       </c>
       <c r="E102" s="3">
-        <v>33200</v>
+        <v>-31400</v>
       </c>
       <c r="F102" s="3">
-        <v>25600</v>
+        <v>31400</v>
       </c>
       <c r="G102" s="3">
-        <v>45300</v>
+        <v>24200</v>
       </c>
       <c r="H102" s="3">
-        <v>71700</v>
+        <v>42800</v>
       </c>
       <c r="I102" s="3">
-        <v>-2900</v>
+        <v>67900</v>
       </c>
       <c r="J102" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="K102" s="3">
         <v>16100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-11200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-11300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>93100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-11600</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/IIJIY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IIJIY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
   <si>
     <t>IIJIY</t>
   </si>
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1761400</v>
+        <v>1960200</v>
       </c>
       <c r="E8" s="3">
-        <v>1612300</v>
+        <v>1794200</v>
       </c>
       <c r="F8" s="3">
-        <v>1444000</v>
+        <v>1607000</v>
       </c>
       <c r="G8" s="3">
-        <v>1359000</v>
+        <v>1512300</v>
       </c>
       <c r="H8" s="3">
-        <v>1304500</v>
+        <v>1451800</v>
       </c>
       <c r="I8" s="3">
-        <v>1227700</v>
+        <v>1366300</v>
       </c>
       <c r="J8" s="3">
-        <v>1124400</v>
+        <v>1251300</v>
       </c>
       <c r="K8" s="3">
         <v>1063500</v>
@@ -765,25 +765,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1353900</v>
+        <v>1506700</v>
       </c>
       <c r="E9" s="3">
-        <v>1885800</v>
+        <v>1383100</v>
       </c>
       <c r="F9" s="3">
-        <v>1114600</v>
+        <v>1240400</v>
       </c>
       <c r="G9" s="3">
-        <v>1102000</v>
+        <v>1226300</v>
       </c>
       <c r="H9" s="3">
-        <v>1096600</v>
+        <v>1220300</v>
       </c>
       <c r="I9" s="3">
-        <v>1042800</v>
+        <v>1160500</v>
       </c>
       <c r="J9" s="3">
-        <v>1871400</v>
+        <v>2082500</v>
       </c>
       <c r="K9" s="3">
         <v>893300</v>
@@ -807,25 +807,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>407500</v>
+        <v>453400</v>
       </c>
       <c r="E10" s="3">
-        <v>-273500</v>
+        <v>411100</v>
       </c>
       <c r="F10" s="3">
-        <v>329400</v>
+        <v>366600</v>
       </c>
       <c r="G10" s="3">
-        <v>257000</v>
+        <v>286000</v>
       </c>
       <c r="H10" s="3">
-        <v>207900</v>
+        <v>231400</v>
       </c>
       <c r="I10" s="3">
-        <v>184900</v>
+        <v>205700</v>
       </c>
       <c r="J10" s="3">
-        <v>-747000</v>
+        <v>-831300</v>
       </c>
       <c r="K10" s="3">
         <v>170200</v>
@@ -866,26 +866,26 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>10</v>
+      <c r="D12" s="3">
+        <v>4500</v>
       </c>
       <c r="E12" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F12" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G12" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H12" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I12" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J12" s="3">
         <v>3500</v>
-      </c>
-      <c r="F12" s="3">
-        <v>3200</v>
-      </c>
-      <c r="G12" s="3">
-        <v>3000</v>
-      </c>
-      <c r="H12" s="3">
-        <v>2800</v>
-      </c>
-      <c r="I12" s="3">
-        <v>2800</v>
-      </c>
-      <c r="J12" s="3">
-        <v>3100</v>
       </c>
       <c r="K12" s="3">
         <v>3100</v>
@@ -950,26 +950,26 @@
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>10</v>
+      <c r="D14" s="3">
+        <v>1300</v>
       </c>
       <c r="E14" s="3">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="F14" s="3">
-        <v>8900</v>
+        <v>10000</v>
       </c>
       <c r="G14" s="3">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="H14" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="I14" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="J14" s="3">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="K14" s="3">
         <v>200</v>
@@ -992,26 +992,26 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>10</v>
+      <c r="D15" s="3">
+        <v>23400</v>
       </c>
       <c r="E15" s="3">
-        <v>19600</v>
+        <v>21900</v>
       </c>
       <c r="F15" s="3">
-        <v>19900</v>
+        <v>22200</v>
       </c>
       <c r="G15" s="3">
-        <v>18100</v>
+        <v>20200</v>
       </c>
       <c r="H15" s="3">
-        <v>18100</v>
+        <v>20200</v>
       </c>
       <c r="I15" s="3">
-        <v>8200</v>
+        <v>9100</v>
       </c>
       <c r="J15" s="3">
-        <v>8000</v>
+        <v>8900</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>10</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1576200</v>
+        <v>1754100</v>
       </c>
       <c r="E17" s="3">
-        <v>1438600</v>
+        <v>1601000</v>
       </c>
       <c r="F17" s="3">
-        <v>1301300</v>
+        <v>1448200</v>
       </c>
       <c r="G17" s="3">
-        <v>1265800</v>
+        <v>1408700</v>
       </c>
       <c r="H17" s="3">
-        <v>1249700</v>
+        <v>1390700</v>
       </c>
       <c r="I17" s="3">
-        <v>1189300</v>
+        <v>1323500</v>
       </c>
       <c r="J17" s="3">
-        <v>1081200</v>
+        <v>1203200</v>
       </c>
       <c r="K17" s="3">
         <v>1029100</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>185200</v>
+        <v>206100</v>
       </c>
       <c r="E18" s="3">
-        <v>173700</v>
+        <v>193300</v>
       </c>
       <c r="F18" s="3">
-        <v>142700</v>
+        <v>158800</v>
       </c>
       <c r="G18" s="3">
-        <v>93100</v>
+        <v>103600</v>
       </c>
       <c r="H18" s="3">
-        <v>54900</v>
+        <v>61100</v>
       </c>
       <c r="I18" s="3">
-        <v>38400</v>
+        <v>42800</v>
       </c>
       <c r="J18" s="3">
-        <v>43200</v>
+        <v>48100</v>
       </c>
       <c r="K18" s="3">
         <v>34400</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-600</v>
+        <v>3300</v>
       </c>
       <c r="E20" s="3">
-        <v>3700</v>
+        <v>4100</v>
       </c>
       <c r="F20" s="3">
-        <v>14700</v>
+        <v>16400</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>-5600</v>
+        <v>-6200</v>
       </c>
       <c r="I20" s="3">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="J20" s="3">
-        <v>5600</v>
+        <v>6300</v>
       </c>
       <c r="K20" s="3">
         <v>4200</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>371200</v>
+        <v>416000</v>
       </c>
       <c r="E21" s="3">
-        <v>360900</v>
+        <v>400500</v>
       </c>
       <c r="F21" s="3">
-        <v>338600</v>
+        <v>375700</v>
       </c>
       <c r="G21" s="3">
-        <v>271300</v>
+        <v>300800</v>
       </c>
       <c r="H21" s="3">
-        <v>231000</v>
+        <v>255900</v>
       </c>
       <c r="I21" s="3">
-        <v>139600</v>
+        <v>154700</v>
       </c>
       <c r="J21" s="3">
-        <v>134300</v>
+        <v>148900</v>
       </c>
       <c r="K21" s="3">
         <v>112400</v>
@@ -1235,26 +1235,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>10</v>
+      <c r="D22" s="3">
+        <v>4000</v>
       </c>
       <c r="E22" s="3">
-        <v>3200</v>
+        <v>3500</v>
       </c>
       <c r="F22" s="3">
-        <v>3300</v>
+        <v>3600</v>
       </c>
       <c r="G22" s="3">
-        <v>3500</v>
+        <v>3900</v>
       </c>
       <c r="H22" s="3">
-        <v>3600</v>
+        <v>4000</v>
       </c>
       <c r="I22" s="3">
-        <v>2700</v>
+        <v>3100</v>
       </c>
       <c r="J22" s="3">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="K22" s="3">
         <v>2000</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>184600</v>
+        <v>205400</v>
       </c>
       <c r="E23" s="3">
-        <v>174200</v>
+        <v>193900</v>
       </c>
       <c r="F23" s="3">
-        <v>154200</v>
+        <v>171600</v>
       </c>
       <c r="G23" s="3">
-        <v>89500</v>
+        <v>99600</v>
       </c>
       <c r="H23" s="3">
-        <v>45700</v>
+        <v>50800</v>
       </c>
       <c r="I23" s="3">
-        <v>37300</v>
+        <v>41500</v>
       </c>
       <c r="J23" s="3">
-        <v>43800</v>
+        <v>48800</v>
       </c>
       <c r="K23" s="3">
         <v>36600</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>57200</v>
+        <v>63600</v>
       </c>
       <c r="E24" s="3">
-        <v>53100</v>
+        <v>59000</v>
       </c>
       <c r="F24" s="3">
-        <v>53300</v>
+        <v>59400</v>
       </c>
       <c r="G24" s="3">
-        <v>27000</v>
+        <v>30100</v>
       </c>
       <c r="H24" s="3">
-        <v>18900</v>
+        <v>21100</v>
       </c>
       <c r="I24" s="3">
-        <v>13700</v>
+        <v>15200</v>
       </c>
       <c r="J24" s="3">
-        <v>14700</v>
+        <v>16300</v>
       </c>
       <c r="K24" s="3">
         <v>15000</v>
@@ -1404,25 +1404,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>127400</v>
+        <v>141800</v>
       </c>
       <c r="E26" s="3">
-        <v>121200</v>
+        <v>134900</v>
       </c>
       <c r="F26" s="3">
-        <v>100800</v>
+        <v>112200</v>
       </c>
       <c r="G26" s="3">
-        <v>62500</v>
+        <v>69600</v>
       </c>
       <c r="H26" s="3">
-        <v>26800</v>
+        <v>29800</v>
       </c>
       <c r="I26" s="3">
-        <v>23600</v>
+        <v>26300</v>
       </c>
       <c r="J26" s="3">
-        <v>29200</v>
+        <v>32500</v>
       </c>
       <c r="K26" s="3">
         <v>21600</v>
@@ -1446,25 +1446,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>126500</v>
+        <v>140800</v>
       </c>
       <c r="E27" s="3">
-        <v>120300</v>
+        <v>133800</v>
       </c>
       <c r="F27" s="3">
-        <v>100000</v>
+        <v>111300</v>
       </c>
       <c r="G27" s="3">
-        <v>62000</v>
+        <v>69000</v>
       </c>
       <c r="H27" s="3">
-        <v>25600</v>
+        <v>28400</v>
       </c>
       <c r="I27" s="3">
-        <v>22500</v>
+        <v>25000</v>
       </c>
       <c r="J27" s="3">
-        <v>29000</v>
+        <v>32200</v>
       </c>
       <c r="K27" s="3">
         <v>21300</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>600</v>
+        <v>-3300</v>
       </c>
       <c r="E32" s="3">
-        <v>-3700</v>
+        <v>-4100</v>
       </c>
       <c r="F32" s="3">
-        <v>-14700</v>
+        <v>-16400</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>5600</v>
+        <v>6200</v>
       </c>
       <c r="I32" s="3">
-        <v>-1600</v>
+        <v>-1800</v>
       </c>
       <c r="J32" s="3">
-        <v>-5600</v>
+        <v>-6300</v>
       </c>
       <c r="K32" s="3">
         <v>-4200</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>126500</v>
+        <v>140800</v>
       </c>
       <c r="E33" s="3">
-        <v>120300</v>
+        <v>133800</v>
       </c>
       <c r="F33" s="3">
-        <v>100000</v>
+        <v>111300</v>
       </c>
       <c r="G33" s="3">
-        <v>62000</v>
+        <v>69000</v>
       </c>
       <c r="H33" s="3">
-        <v>25600</v>
+        <v>28400</v>
       </c>
       <c r="I33" s="3">
-        <v>22500</v>
+        <v>25000</v>
       </c>
       <c r="J33" s="3">
-        <v>29100</v>
+        <v>32400</v>
       </c>
       <c r="K33" s="3">
         <v>21300</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>126500</v>
+        <v>140800</v>
       </c>
       <c r="E35" s="3">
-        <v>120300</v>
+        <v>133800</v>
       </c>
       <c r="F35" s="3">
-        <v>100000</v>
+        <v>111300</v>
       </c>
       <c r="G35" s="3">
-        <v>62000</v>
+        <v>69000</v>
       </c>
       <c r="H35" s="3">
-        <v>25600</v>
+        <v>28400</v>
       </c>
       <c r="I35" s="3">
-        <v>22500</v>
+        <v>25000</v>
       </c>
       <c r="J35" s="3">
-        <v>29100</v>
+        <v>32400</v>
       </c>
       <c r="K35" s="3">
         <v>21300</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>290100</v>
+        <v>322900</v>
       </c>
       <c r="E41" s="3">
-        <v>271000</v>
+        <v>301600</v>
       </c>
       <c r="F41" s="3">
-        <v>302400</v>
+        <v>336500</v>
       </c>
       <c r="G41" s="3">
-        <v>270900</v>
+        <v>301500</v>
       </c>
       <c r="H41" s="3">
-        <v>246700</v>
+        <v>274600</v>
       </c>
       <c r="I41" s="3">
-        <v>203900</v>
+        <v>226900</v>
       </c>
       <c r="J41" s="3">
-        <v>272600</v>
+        <v>303300</v>
       </c>
       <c r="K41" s="3">
         <v>148000</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>9800</v>
+        <v>10900</v>
       </c>
       <c r="E42" s="3">
-        <v>12200</v>
+        <v>13600</v>
       </c>
       <c r="F42" s="3">
-        <v>8300</v>
+        <v>9200</v>
       </c>
       <c r="G42" s="3">
-        <v>12600</v>
+        <v>14000</v>
       </c>
       <c r="H42" s="3">
-        <v>17000</v>
+        <v>19000</v>
       </c>
       <c r="I42" s="3">
-        <v>10100</v>
+        <v>11200</v>
       </c>
       <c r="J42" s="3">
-        <v>24000</v>
+        <v>26700</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>10</v>
@@ -1991,25 +1991,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>311300</v>
+        <v>346400</v>
       </c>
       <c r="E43" s="3">
-        <v>541400</v>
+        <v>602500</v>
       </c>
       <c r="F43" s="3">
-        <v>252100</v>
+        <v>280600</v>
       </c>
       <c r="G43" s="3">
-        <v>230200</v>
+        <v>256200</v>
       </c>
       <c r="H43" s="3">
-        <v>210400</v>
+        <v>234200</v>
       </c>
       <c r="I43" s="3">
-        <v>212900</v>
+        <v>237000</v>
       </c>
       <c r="J43" s="3">
-        <v>404500</v>
+        <v>450100</v>
       </c>
       <c r="K43" s="3">
         <v>184500</v>
@@ -2033,25 +2033,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>20600</v>
+        <v>22900</v>
       </c>
       <c r="E44" s="3">
-        <v>40700</v>
+        <v>45300</v>
       </c>
       <c r="F44" s="3">
-        <v>16600</v>
+        <v>18500</v>
       </c>
       <c r="G44" s="3">
-        <v>13900</v>
+        <v>15400</v>
       </c>
       <c r="H44" s="3">
-        <v>15800</v>
+        <v>17600</v>
       </c>
       <c r="I44" s="3">
-        <v>21700</v>
+        <v>24200</v>
       </c>
       <c r="J44" s="3">
-        <v>20800</v>
+        <v>23100</v>
       </c>
       <c r="K44" s="3">
         <v>18900</v>
@@ -2075,25 +2075,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>133100</v>
+        <v>148100</v>
       </c>
       <c r="E45" s="3">
-        <v>99400</v>
+        <v>110600</v>
       </c>
       <c r="F45" s="3">
-        <v>87200</v>
+        <v>97100</v>
       </c>
       <c r="G45" s="3">
-        <v>68300</v>
+        <v>76000</v>
       </c>
       <c r="H45" s="3">
-        <v>62500</v>
+        <v>69500</v>
       </c>
       <c r="I45" s="3">
-        <v>55200</v>
+        <v>61400</v>
       </c>
       <c r="J45" s="3">
-        <v>126900</v>
+        <v>141200</v>
       </c>
       <c r="K45" s="3">
         <v>78200</v>
@@ -2117,25 +2117,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>764900</v>
+        <v>851200</v>
       </c>
       <c r="E46" s="3">
-        <v>680600</v>
+        <v>757400</v>
       </c>
       <c r="F46" s="3">
-        <v>666600</v>
+        <v>741800</v>
       </c>
       <c r="G46" s="3">
-        <v>595900</v>
+        <v>663200</v>
       </c>
       <c r="H46" s="3">
-        <v>552400</v>
+        <v>614800</v>
       </c>
       <c r="I46" s="3">
-        <v>503800</v>
+        <v>560700</v>
       </c>
       <c r="J46" s="3">
-        <v>420100</v>
+        <v>467500</v>
       </c>
       <c r="K46" s="3">
         <v>429500</v>
@@ -2159,25 +2159,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>222400</v>
+        <v>247500</v>
       </c>
       <c r="E47" s="3">
-        <v>189300</v>
+        <v>210700</v>
       </c>
       <c r="F47" s="3">
-        <v>175800</v>
+        <v>195600</v>
       </c>
       <c r="G47" s="3">
-        <v>168600</v>
+        <v>187600</v>
       </c>
       <c r="H47" s="3">
-        <v>119400</v>
+        <v>132900</v>
       </c>
       <c r="I47" s="3">
-        <v>137400</v>
+        <v>152900</v>
       </c>
       <c r="J47" s="3">
-        <v>179700</v>
+        <v>200000</v>
       </c>
       <c r="K47" s="3">
         <v>20800</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>448600</v>
+        <v>499200</v>
       </c>
       <c r="E48" s="3">
-        <v>893100</v>
+        <v>993900</v>
       </c>
       <c r="F48" s="3">
-        <v>400200</v>
+        <v>445300</v>
       </c>
       <c r="G48" s="3">
-        <v>432500</v>
+        <v>481300</v>
       </c>
       <c r="H48" s="3">
-        <v>433600</v>
+        <v>482500</v>
       </c>
       <c r="I48" s="3">
-        <v>211400</v>
+        <v>235300</v>
       </c>
       <c r="J48" s="3">
-        <v>510000</v>
+        <v>567600</v>
       </c>
       <c r="K48" s="3">
         <v>268100</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>183000</v>
+        <v>203700</v>
       </c>
       <c r="E49" s="3">
-        <v>337800</v>
+        <v>375900</v>
       </c>
       <c r="F49" s="3">
-        <v>165300</v>
+        <v>183900</v>
       </c>
       <c r="G49" s="3">
-        <v>147000</v>
+        <v>163600</v>
       </c>
       <c r="H49" s="3">
-        <v>155400</v>
+        <v>173000</v>
       </c>
       <c r="I49" s="3">
-        <v>158900</v>
+        <v>176800</v>
       </c>
       <c r="J49" s="3">
-        <v>208200</v>
+        <v>231700</v>
       </c>
       <c r="K49" s="3">
         <v>62400</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>127400</v>
+        <v>141800</v>
       </c>
       <c r="E52" s="3">
-        <v>86100</v>
+        <v>95800</v>
       </c>
       <c r="F52" s="3">
-        <v>71100</v>
+        <v>79100</v>
       </c>
       <c r="G52" s="3">
-        <v>64500</v>
+        <v>71800</v>
       </c>
       <c r="H52" s="3">
-        <v>56700</v>
+        <v>63100</v>
       </c>
       <c r="I52" s="3">
-        <v>55800</v>
+        <v>62100</v>
       </c>
       <c r="J52" s="3">
-        <v>222300</v>
+        <v>247400</v>
       </c>
       <c r="K52" s="3">
         <v>145300</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1746300</v>
+        <v>1943400</v>
       </c>
       <c r="E54" s="3">
-        <v>1571500</v>
+        <v>1748900</v>
       </c>
       <c r="F54" s="3">
-        <v>1478900</v>
+        <v>1645800</v>
       </c>
       <c r="G54" s="3">
-        <v>1408600</v>
+        <v>1567500</v>
       </c>
       <c r="H54" s="3">
-        <v>1317600</v>
+        <v>1466300</v>
       </c>
       <c r="I54" s="3">
-        <v>1067300</v>
+        <v>1187800</v>
       </c>
       <c r="J54" s="3">
-        <v>989900</v>
+        <v>1101700</v>
       </c>
       <c r="K54" s="3">
         <v>926000</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>162300</v>
+        <v>79100</v>
       </c>
       <c r="E57" s="3">
-        <v>207300</v>
+        <v>230700</v>
       </c>
       <c r="F57" s="3">
-        <v>55700</v>
+        <v>61900</v>
       </c>
       <c r="G57" s="3">
-        <v>40800</v>
+        <v>45400</v>
       </c>
       <c r="H57" s="3">
-        <v>38100</v>
+        <v>42400</v>
       </c>
       <c r="I57" s="3">
-        <v>49800</v>
+        <v>55500</v>
       </c>
       <c r="J57" s="3">
-        <v>130000</v>
+        <v>144700</v>
       </c>
       <c r="K57" s="3">
         <v>98800</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>192200</v>
+        <v>213900</v>
       </c>
       <c r="E58" s="3">
-        <v>214700</v>
+        <v>239000</v>
       </c>
       <c r="F58" s="3">
-        <v>104400</v>
+        <v>116200</v>
       </c>
       <c r="G58" s="3">
-        <v>118400</v>
+        <v>131800</v>
       </c>
       <c r="H58" s="3">
-        <v>99400</v>
+        <v>110600</v>
       </c>
       <c r="I58" s="3">
-        <v>122900</v>
+        <v>136800</v>
       </c>
       <c r="J58" s="3">
-        <v>190100</v>
+        <v>211600</v>
       </c>
       <c r="K58" s="3">
         <v>94800</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>273000</v>
+        <v>405300</v>
       </c>
       <c r="E59" s="3">
-        <v>324400</v>
+        <v>361000</v>
       </c>
       <c r="F59" s="3">
-        <v>329700</v>
+        <v>367000</v>
       </c>
       <c r="G59" s="3">
-        <v>308200</v>
+        <v>343000</v>
       </c>
       <c r="H59" s="3">
-        <v>281500</v>
+        <v>313300</v>
       </c>
       <c r="I59" s="3">
-        <v>164800</v>
+        <v>183400</v>
       </c>
       <c r="J59" s="3">
-        <v>217600</v>
+        <v>242100</v>
       </c>
       <c r="K59" s="3">
         <v>75900</v>
@@ -2657,25 +2657,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>627500</v>
+        <v>698300</v>
       </c>
       <c r="E60" s="3">
-        <v>496800</v>
+        <v>552800</v>
       </c>
       <c r="F60" s="3">
-        <v>489800</v>
+        <v>545100</v>
       </c>
       <c r="G60" s="3">
-        <v>467400</v>
+        <v>520100</v>
       </c>
       <c r="H60" s="3">
-        <v>419100</v>
+        <v>466400</v>
       </c>
       <c r="I60" s="3">
-        <v>337500</v>
+        <v>375600</v>
       </c>
       <c r="J60" s="3">
-        <v>268800</v>
+        <v>299200</v>
       </c>
       <c r="K60" s="3">
         <v>269500</v>
@@ -2702,22 +2702,22 @@
         <v>300</v>
       </c>
       <c r="E61" s="3">
-        <v>23000</v>
+        <v>25600</v>
       </c>
       <c r="F61" s="3">
-        <v>35100</v>
+        <v>39100</v>
       </c>
       <c r="G61" s="3">
-        <v>44700</v>
+        <v>49700</v>
       </c>
       <c r="H61" s="3">
-        <v>77600</v>
+        <v>86400</v>
       </c>
       <c r="I61" s="3">
-        <v>162800</v>
+        <v>181200</v>
       </c>
       <c r="J61" s="3">
-        <v>168600</v>
+        <v>187600</v>
       </c>
       <c r="K61" s="3">
         <v>127300</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>308000</v>
+        <v>342800</v>
       </c>
       <c r="E62" s="3">
-        <v>490700</v>
+        <v>546100</v>
       </c>
       <c r="F62" s="3">
-        <v>286500</v>
+        <v>318800</v>
       </c>
       <c r="G62" s="3">
-        <v>316100</v>
+        <v>351800</v>
       </c>
       <c r="H62" s="3">
-        <v>310100</v>
+        <v>345100</v>
       </c>
       <c r="I62" s="3">
-        <v>75000</v>
+        <v>83400</v>
       </c>
       <c r="J62" s="3">
-        <v>142000</v>
+        <v>158000</v>
       </c>
       <c r="K62" s="3">
         <v>75100</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>944000</v>
+        <v>1050500</v>
       </c>
       <c r="E66" s="3">
-        <v>817100</v>
+        <v>909300</v>
       </c>
       <c r="F66" s="3">
-        <v>818400</v>
+        <v>910800</v>
       </c>
       <c r="G66" s="3">
-        <v>834600</v>
+        <v>928800</v>
       </c>
       <c r="H66" s="3">
-        <v>813100</v>
+        <v>904900</v>
       </c>
       <c r="I66" s="3">
-        <v>580700</v>
+        <v>646200</v>
       </c>
       <c r="J66" s="3">
-        <v>514400</v>
+        <v>572500</v>
       </c>
       <c r="K66" s="3">
         <v>476200</v>
@@ -3137,25 +3137,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>418600</v>
+        <v>465900</v>
       </c>
       <c r="E72" s="3">
-        <v>326700</v>
+        <v>363500</v>
       </c>
       <c r="F72" s="3">
-        <v>236200</v>
+        <v>262900</v>
       </c>
       <c r="G72" s="3">
-        <v>159800</v>
+        <v>177800</v>
       </c>
       <c r="H72" s="3">
-        <v>105300</v>
+        <v>117200</v>
       </c>
       <c r="I72" s="3">
-        <v>78700</v>
+        <v>87600</v>
       </c>
       <c r="J72" s="3">
-        <v>115400</v>
+        <v>128400</v>
       </c>
       <c r="K72" s="3">
         <v>30400</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>802300</v>
+        <v>892800</v>
       </c>
       <c r="E76" s="3">
-        <v>754400</v>
+        <v>839500</v>
       </c>
       <c r="F76" s="3">
-        <v>660500</v>
+        <v>735000</v>
       </c>
       <c r="G76" s="3">
-        <v>573900</v>
+        <v>638700</v>
       </c>
       <c r="H76" s="3">
-        <v>504500</v>
+        <v>561400</v>
       </c>
       <c r="I76" s="3">
-        <v>486600</v>
+        <v>541500</v>
       </c>
       <c r="J76" s="3">
-        <v>475500</v>
+        <v>529200</v>
       </c>
       <c r="K76" s="3">
         <v>449800</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>126500</v>
+        <v>140800</v>
       </c>
       <c r="E81" s="3">
-        <v>120300</v>
+        <v>133800</v>
       </c>
       <c r="F81" s="3">
-        <v>100000</v>
+        <v>111300</v>
       </c>
       <c r="G81" s="3">
-        <v>62000</v>
+        <v>69000</v>
       </c>
       <c r="H81" s="3">
-        <v>25600</v>
+        <v>28400</v>
       </c>
       <c r="I81" s="3">
-        <v>22500</v>
+        <v>25000</v>
       </c>
       <c r="J81" s="3">
-        <v>29100</v>
+        <v>32400</v>
       </c>
       <c r="K81" s="3">
         <v>21300</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>186900</v>
+        <v>208000</v>
       </c>
       <c r="E83" s="3">
-        <v>183800</v>
+        <v>204500</v>
       </c>
       <c r="F83" s="3">
-        <v>181500</v>
+        <v>202000</v>
       </c>
       <c r="G83" s="3">
-        <v>178500</v>
+        <v>198600</v>
       </c>
       <c r="H83" s="3">
-        <v>182000</v>
+        <v>202500</v>
       </c>
       <c r="I83" s="3">
-        <v>99700</v>
+        <v>111000</v>
       </c>
       <c r="J83" s="3">
-        <v>85600</v>
+        <v>95200</v>
       </c>
       <c r="K83" s="3">
         <v>73400</v>
@@ -3748,25 +3748,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>260200</v>
+        <v>289500</v>
       </c>
       <c r="E89" s="3">
-        <v>245800</v>
+        <v>273600</v>
       </c>
       <c r="F89" s="3">
-        <v>278000</v>
+        <v>309400</v>
       </c>
       <c r="G89" s="3">
-        <v>258700</v>
+        <v>287900</v>
       </c>
       <c r="H89" s="3">
-        <v>213100</v>
+        <v>237100</v>
       </c>
       <c r="I89" s="3">
-        <v>160500</v>
+        <v>178600</v>
       </c>
       <c r="J89" s="3">
-        <v>93600</v>
+        <v>104100</v>
       </c>
       <c r="K89" s="3">
         <v>49700</v>
@@ -3808,25 +3808,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-74900</v>
+        <v>-83400</v>
       </c>
       <c r="E91" s="3">
-        <v>-75200</v>
+        <v>-83700</v>
       </c>
       <c r="F91" s="3">
-        <v>-43300</v>
+        <v>-48200</v>
       </c>
       <c r="G91" s="3">
-        <v>-40800</v>
+        <v>-45400</v>
       </c>
       <c r="H91" s="3">
-        <v>-45900</v>
+        <v>-51100</v>
       </c>
       <c r="I91" s="3">
-        <v>-45200</v>
+        <v>-50300</v>
       </c>
       <c r="J91" s="3">
-        <v>-171400</v>
+        <v>-190700</v>
       </c>
       <c r="K91" s="3">
         <v>-71600</v>
@@ -3934,25 +3934,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-114400</v>
+        <v>-127300</v>
       </c>
       <c r="E94" s="3">
-        <v>-117300</v>
+        <v>-130500</v>
       </c>
       <c r="F94" s="3">
-        <v>-75500</v>
+        <v>-84100</v>
       </c>
       <c r="G94" s="3">
-        <v>-84300</v>
+        <v>-93800</v>
       </c>
       <c r="H94" s="3">
-        <v>-46300</v>
+        <v>-51600</v>
       </c>
       <c r="I94" s="3">
-        <v>-55400</v>
+        <v>-61700</v>
       </c>
       <c r="J94" s="3">
-        <v>-91200</v>
+        <v>-101500</v>
       </c>
       <c r="K94" s="3">
         <v>-49700</v>
@@ -3994,25 +3994,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-36300</v>
+        <v>-40300</v>
       </c>
       <c r="E96" s="3">
-        <v>-31300</v>
+        <v>-34800</v>
       </c>
       <c r="F96" s="3">
-        <v>-24500</v>
+        <v>-27200</v>
       </c>
       <c r="G96" s="3">
-        <v>-9800</v>
+        <v>-10900</v>
       </c>
       <c r="H96" s="3">
-        <v>-7800</v>
+        <v>-8600</v>
       </c>
       <c r="I96" s="3">
-        <v>-7800</v>
+        <v>-8600</v>
       </c>
       <c r="J96" s="3">
-        <v>-7800</v>
+        <v>-8600</v>
       </c>
       <c r="K96" s="3">
         <v>-7600</v>
@@ -4162,25 +4162,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-132700</v>
+        <v>-147700</v>
       </c>
       <c r="E100" s="3">
-        <v>-164200</v>
+        <v>-182700</v>
       </c>
       <c r="F100" s="3">
-        <v>-174100</v>
+        <v>-193800</v>
       </c>
       <c r="G100" s="3">
-        <v>-150700</v>
+        <v>-167700</v>
       </c>
       <c r="H100" s="3">
-        <v>-123500</v>
+        <v>-137400</v>
       </c>
       <c r="I100" s="3">
-        <v>-37600</v>
+        <v>-41800</v>
       </c>
       <c r="J100" s="3">
-        <v>-4600</v>
+        <v>-5100</v>
       </c>
       <c r="K100" s="3">
         <v>16800</v>
@@ -4204,16 +4204,16 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>6000</v>
+        <v>6700</v>
       </c>
       <c r="E101" s="3">
-        <v>4300</v>
+        <v>4700</v>
       </c>
       <c r="F101" s="3">
-        <v>3100</v>
+        <v>3400</v>
       </c>
       <c r="G101" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="H101" s="3">
         <v>-400</v>
@@ -4246,25 +4246,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>19200</v>
+        <v>21300</v>
       </c>
       <c r="E102" s="3">
-        <v>-31400</v>
+        <v>-34900</v>
       </c>
       <c r="F102" s="3">
-        <v>31400</v>
+        <v>35000</v>
       </c>
       <c r="G102" s="3">
-        <v>24200</v>
+        <v>26900</v>
       </c>
       <c r="H102" s="3">
-        <v>42800</v>
+        <v>47700</v>
       </c>
       <c r="I102" s="3">
-        <v>67900</v>
+        <v>75500</v>
       </c>
       <c r="J102" s="3">
-        <v>-2700</v>
+        <v>-3000</v>
       </c>
       <c r="K102" s="3">
         <v>16100</v>

--- a/AAII_Financials/Yearly/IIJIY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IIJIY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>IIJIY</t>
   </si>
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1960200</v>
+        <v>1825300</v>
       </c>
       <c r="E8" s="3">
-        <v>1794200</v>
+        <v>1901000</v>
       </c>
       <c r="F8" s="3">
-        <v>1607000</v>
+        <v>1863900</v>
       </c>
       <c r="G8" s="3">
-        <v>1512300</v>
+        <v>1925900</v>
       </c>
       <c r="H8" s="3">
-        <v>1451800</v>
+        <v>1900300</v>
       </c>
       <c r="I8" s="3">
-        <v>1366300</v>
+        <v>1736600</v>
       </c>
       <c r="J8" s="3">
-        <v>1251300</v>
+        <v>1657600</v>
       </c>
       <c r="K8" s="3">
         <v>1063500</v>
@@ -765,25 +765,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1506700</v>
+        <v>1403000</v>
       </c>
       <c r="E9" s="3">
-        <v>1383100</v>
+        <v>1465400</v>
       </c>
       <c r="F9" s="3">
-        <v>1240400</v>
+        <v>1438700</v>
       </c>
       <c r="G9" s="3">
-        <v>1226300</v>
+        <v>1561700</v>
       </c>
       <c r="H9" s="3">
-        <v>1220300</v>
+        <v>1597400</v>
       </c>
       <c r="I9" s="3">
-        <v>1160500</v>
+        <v>1475100</v>
       </c>
       <c r="J9" s="3">
-        <v>2082500</v>
+        <v>1391800</v>
       </c>
       <c r="K9" s="3">
         <v>893300</v>
@@ -807,25 +807,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>453400</v>
+        <v>422200</v>
       </c>
       <c r="E10" s="3">
-        <v>411100</v>
+        <v>435600</v>
       </c>
       <c r="F10" s="3">
-        <v>366600</v>
+        <v>425100</v>
       </c>
       <c r="G10" s="3">
-        <v>286000</v>
+        <v>364200</v>
       </c>
       <c r="H10" s="3">
-        <v>231400</v>
+        <v>302900</v>
       </c>
       <c r="I10" s="3">
-        <v>205700</v>
+        <v>261500</v>
       </c>
       <c r="J10" s="3">
-        <v>-831300</v>
+        <v>265800</v>
       </c>
       <c r="K10" s="3">
         <v>170200</v>
@@ -867,25 +867,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>4500</v>
+        <v>4200</v>
       </c>
       <c r="E12" s="3">
-        <v>3900</v>
+        <v>4100</v>
       </c>
       <c r="F12" s="3">
-        <v>3600</v>
+        <v>4200</v>
       </c>
       <c r="G12" s="3">
-        <v>3400</v>
+        <v>4300</v>
       </c>
       <c r="H12" s="3">
-        <v>3100</v>
+        <v>4100</v>
       </c>
       <c r="I12" s="3">
-        <v>3200</v>
+        <v>4000</v>
       </c>
       <c r="J12" s="3">
-        <v>3500</v>
+        <v>4600</v>
       </c>
       <c r="K12" s="3">
         <v>3100</v>
@@ -951,25 +951,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>1300</v>
+        <v>-100</v>
       </c>
       <c r="E14" s="3">
-        <v>2100</v>
+        <v>-3200</v>
       </c>
       <c r="F14" s="3">
-        <v>10000</v>
+        <v>-23400</v>
       </c>
       <c r="G14" s="3">
-        <v>2800</v>
+        <v>1400</v>
       </c>
       <c r="H14" s="3">
-        <v>1300</v>
+        <v>2600</v>
       </c>
       <c r="I14" s="3">
-        <v>2200</v>
+        <v>-900</v>
       </c>
       <c r="J14" s="3">
-        <v>1600</v>
+        <v>-9000</v>
       </c>
       <c r="K14" s="3">
         <v>200</v>
@@ -993,25 +993,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>23400</v>
+        <v>21800</v>
       </c>
       <c r="E15" s="3">
-        <v>21900</v>
+        <v>23200</v>
       </c>
       <c r="F15" s="3">
-        <v>22200</v>
+        <v>25700</v>
       </c>
       <c r="G15" s="3">
-        <v>20200</v>
+        <v>25700</v>
       </c>
       <c r="H15" s="3">
-        <v>20200</v>
+        <v>26400</v>
       </c>
       <c r="I15" s="3">
-        <v>9100</v>
+        <v>11500</v>
       </c>
       <c r="J15" s="3">
-        <v>8900</v>
+        <v>84900</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>10</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1754100</v>
+        <v>1633000</v>
       </c>
       <c r="E17" s="3">
-        <v>1601000</v>
+        <v>1697600</v>
       </c>
       <c r="F17" s="3">
-        <v>1448200</v>
+        <v>1668800</v>
       </c>
       <c r="G17" s="3">
-        <v>1408700</v>
+        <v>1792100</v>
       </c>
       <c r="H17" s="3">
-        <v>1390700</v>
+        <v>1819900</v>
       </c>
       <c r="I17" s="3">
-        <v>1323500</v>
+        <v>1679500</v>
       </c>
       <c r="J17" s="3">
-        <v>1203200</v>
+        <v>1594000</v>
       </c>
       <c r="K17" s="3">
         <v>1029100</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>206100</v>
+        <v>192300</v>
       </c>
       <c r="E18" s="3">
-        <v>193300</v>
+        <v>203400</v>
       </c>
       <c r="F18" s="3">
-        <v>158800</v>
+        <v>195000</v>
       </c>
       <c r="G18" s="3">
-        <v>103600</v>
+        <v>133800</v>
       </c>
       <c r="H18" s="3">
-        <v>61100</v>
+        <v>80400</v>
       </c>
       <c r="I18" s="3">
-        <v>42800</v>
+        <v>57100</v>
       </c>
       <c r="J18" s="3">
-        <v>48100</v>
+        <v>63700</v>
       </c>
       <c r="K18" s="3">
         <v>34400</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>3300</v>
+        <v>-300</v>
       </c>
       <c r="E20" s="3">
-        <v>4100</v>
+        <v>-1300</v>
       </c>
       <c r="F20" s="3">
-        <v>16400</v>
+        <v>16200</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="H20" s="3">
-        <v>-6200</v>
+        <v>7400</v>
       </c>
       <c r="I20" s="3">
-        <v>1800</v>
+        <v>2600</v>
       </c>
       <c r="J20" s="3">
-        <v>6300</v>
+        <v>-3400</v>
       </c>
       <c r="K20" s="3">
         <v>4200</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>416000</v>
+        <v>214400</v>
       </c>
       <c r="E21" s="3">
-        <v>400500</v>
+        <v>227800</v>
       </c>
       <c r="F21" s="3">
-        <v>375700</v>
+        <v>204500</v>
       </c>
       <c r="G21" s="3">
-        <v>300800</v>
+        <v>157700</v>
       </c>
       <c r="H21" s="3">
-        <v>255900</v>
+        <v>99400</v>
       </c>
       <c r="I21" s="3">
-        <v>154700</v>
+        <v>66100</v>
       </c>
       <c r="J21" s="3">
-        <v>148900</v>
+        <v>151900</v>
       </c>
       <c r="K21" s="3">
         <v>112400</v>
@@ -1236,25 +1236,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>4000</v>
+        <v>3700</v>
       </c>
       <c r="E22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F22" s="3">
+        <v>4200</v>
+      </c>
+      <c r="G22" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H22" s="3">
+        <v>5200</v>
+      </c>
+      <c r="I22" s="3">
+        <v>3900</v>
+      </c>
+      <c r="J22" s="3">
         <v>3500</v>
-      </c>
-      <c r="F22" s="3">
-        <v>3600</v>
-      </c>
-      <c r="G22" s="3">
-        <v>3900</v>
-      </c>
-      <c r="H22" s="3">
-        <v>4000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>3100</v>
-      </c>
-      <c r="J22" s="3">
-        <v>5500</v>
       </c>
       <c r="K22" s="3">
         <v>2000</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>191300</v>
+      </c>
+      <c r="E23" s="3">
         <v>205400</v>
       </c>
-      <c r="E23" s="3">
-        <v>193900</v>
-      </c>
       <c r="F23" s="3">
-        <v>171600</v>
+        <v>199000</v>
       </c>
       <c r="G23" s="3">
-        <v>99600</v>
+        <v>126900</v>
       </c>
       <c r="H23" s="3">
-        <v>50800</v>
+        <v>66500</v>
       </c>
       <c r="I23" s="3">
-        <v>41500</v>
+        <v>52700</v>
       </c>
       <c r="J23" s="3">
-        <v>48800</v>
+        <v>75100</v>
       </c>
       <c r="K23" s="3">
         <v>36600</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>63600</v>
+        <v>59200</v>
       </c>
       <c r="E24" s="3">
-        <v>59000</v>
+        <v>62700</v>
       </c>
       <c r="F24" s="3">
-        <v>59400</v>
+        <v>68900</v>
       </c>
       <c r="G24" s="3">
-        <v>30100</v>
+        <v>38300</v>
       </c>
       <c r="H24" s="3">
-        <v>21100</v>
+        <v>27600</v>
       </c>
       <c r="I24" s="3">
-        <v>15200</v>
+        <v>19300</v>
       </c>
       <c r="J24" s="3">
-        <v>16300</v>
+        <v>25400</v>
       </c>
       <c r="K24" s="3">
         <v>15000</v>
@@ -1404,25 +1404,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>141800</v>
+        <v>132100</v>
       </c>
       <c r="E26" s="3">
-        <v>134900</v>
+        <v>142800</v>
       </c>
       <c r="F26" s="3">
-        <v>112200</v>
+        <v>130100</v>
       </c>
       <c r="G26" s="3">
-        <v>69600</v>
+        <v>88600</v>
       </c>
       <c r="H26" s="3">
-        <v>29800</v>
+        <v>39000</v>
       </c>
       <c r="I26" s="3">
-        <v>26300</v>
+        <v>33400</v>
       </c>
       <c r="J26" s="3">
-        <v>32500</v>
+        <v>49700</v>
       </c>
       <c r="K26" s="3">
         <v>21600</v>
@@ -1446,25 +1446,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>140800</v>
+        <v>131100</v>
       </c>
       <c r="E27" s="3">
-        <v>133800</v>
+        <v>141700</v>
       </c>
       <c r="F27" s="3">
-        <v>111300</v>
+        <v>129100</v>
       </c>
       <c r="G27" s="3">
-        <v>69000</v>
+        <v>87800</v>
       </c>
       <c r="H27" s="3">
-        <v>28400</v>
+        <v>37200</v>
       </c>
       <c r="I27" s="3">
-        <v>25000</v>
+        <v>31800</v>
       </c>
       <c r="J27" s="3">
-        <v>32200</v>
+        <v>48100</v>
       </c>
       <c r="K27" s="3">
         <v>21300</v>
@@ -1529,26 +1529,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>10</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>10</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-3300</v>
+        <v>300</v>
       </c>
       <c r="E32" s="3">
-        <v>-4100</v>
+        <v>1300</v>
       </c>
       <c r="F32" s="3">
-        <v>-16400</v>
+        <v>-16200</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="H32" s="3">
-        <v>6200</v>
+        <v>-7400</v>
       </c>
       <c r="I32" s="3">
-        <v>-1800</v>
+        <v>-2600</v>
       </c>
       <c r="J32" s="3">
-        <v>-6300</v>
+        <v>3400</v>
       </c>
       <c r="K32" s="3">
         <v>-4200</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>140800</v>
+        <v>131100</v>
       </c>
       <c r="E33" s="3">
-        <v>133800</v>
+        <v>141700</v>
       </c>
       <c r="F33" s="3">
-        <v>111300</v>
+        <v>129100</v>
       </c>
       <c r="G33" s="3">
-        <v>69000</v>
+        <v>87800</v>
       </c>
       <c r="H33" s="3">
-        <v>28400</v>
+        <v>37200</v>
       </c>
       <c r="I33" s="3">
-        <v>25000</v>
+        <v>31800</v>
       </c>
       <c r="J33" s="3">
-        <v>32400</v>
+        <v>48100</v>
       </c>
       <c r="K33" s="3">
         <v>21300</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>140800</v>
+        <v>131100</v>
       </c>
       <c r="E35" s="3">
-        <v>133800</v>
+        <v>141700</v>
       </c>
       <c r="F35" s="3">
-        <v>111300</v>
+        <v>129100</v>
       </c>
       <c r="G35" s="3">
-        <v>69000</v>
+        <v>87800</v>
       </c>
       <c r="H35" s="3">
-        <v>28400</v>
+        <v>37200</v>
       </c>
       <c r="I35" s="3">
-        <v>25000</v>
+        <v>31800</v>
       </c>
       <c r="J35" s="3">
-        <v>32400</v>
+        <v>48100</v>
       </c>
       <c r="K35" s="3">
         <v>21300</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>322900</v>
+        <v>300600</v>
       </c>
       <c r="E41" s="3">
-        <v>301600</v>
+        <v>319500</v>
       </c>
       <c r="F41" s="3">
-        <v>336500</v>
+        <v>390300</v>
       </c>
       <c r="G41" s="3">
-        <v>301500</v>
+        <v>384000</v>
       </c>
       <c r="H41" s="3">
-        <v>274600</v>
+        <v>359400</v>
       </c>
       <c r="I41" s="3">
-        <v>226900</v>
+        <v>288400</v>
       </c>
       <c r="J41" s="3">
-        <v>303300</v>
+        <v>201500</v>
       </c>
       <c r="K41" s="3">
         <v>148000</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>10900</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>13600</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>9200</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>19000</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>11200</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>26700</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>10</v>
@@ -1991,25 +1991,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>346400</v>
+        <v>302000</v>
       </c>
       <c r="E43" s="3">
-        <v>602500</v>
+        <v>311000</v>
       </c>
       <c r="F43" s="3">
-        <v>280600</v>
+        <v>310000</v>
       </c>
       <c r="G43" s="3">
-        <v>256200</v>
+        <v>314600</v>
       </c>
       <c r="H43" s="3">
-        <v>234200</v>
+        <v>306500</v>
       </c>
       <c r="I43" s="3">
-        <v>237000</v>
+        <v>301200</v>
       </c>
       <c r="J43" s="3">
-        <v>450100</v>
+        <v>299700</v>
       </c>
       <c r="K43" s="3">
         <v>184500</v>
@@ -2033,25 +2033,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>22900</v>
+        <v>21300</v>
       </c>
       <c r="E44" s="3">
-        <v>45300</v>
+        <v>24000</v>
       </c>
       <c r="F44" s="3">
-        <v>18500</v>
+        <v>21500</v>
       </c>
       <c r="G44" s="3">
-        <v>15400</v>
+        <v>19600</v>
       </c>
       <c r="H44" s="3">
-        <v>17600</v>
+        <v>23000</v>
       </c>
       <c r="I44" s="3">
-        <v>24200</v>
+        <v>30700</v>
       </c>
       <c r="J44" s="3">
-        <v>23100</v>
+        <v>16100</v>
       </c>
       <c r="K44" s="3">
         <v>18900</v>
@@ -2075,25 +2075,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>148100</v>
+        <v>35800</v>
       </c>
       <c r="E45" s="3">
-        <v>110600</v>
+        <v>32600</v>
       </c>
       <c r="F45" s="3">
-        <v>97100</v>
+        <v>27100</v>
       </c>
       <c r="G45" s="3">
-        <v>76000</v>
+        <v>30500</v>
       </c>
       <c r="H45" s="3">
-        <v>69500</v>
+        <v>25700</v>
       </c>
       <c r="I45" s="3">
-        <v>61400</v>
+        <v>15500</v>
       </c>
       <c r="J45" s="3">
-        <v>141200</v>
+        <v>35700</v>
       </c>
       <c r="K45" s="3">
         <v>78200</v>
@@ -2117,25 +2117,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>851200</v>
+        <v>792600</v>
       </c>
       <c r="E46" s="3">
-        <v>757400</v>
+        <v>802500</v>
       </c>
       <c r="F46" s="3">
-        <v>741800</v>
+        <v>860400</v>
       </c>
       <c r="G46" s="3">
-        <v>663200</v>
+        <v>844500</v>
       </c>
       <c r="H46" s="3">
-        <v>614800</v>
+        <v>804700</v>
       </c>
       <c r="I46" s="3">
-        <v>560700</v>
+        <v>712700</v>
       </c>
       <c r="J46" s="3">
-        <v>467500</v>
+        <v>632600</v>
       </c>
       <c r="K46" s="3">
         <v>429500</v>
@@ -2159,25 +2159,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>247500</v>
+        <v>360600</v>
       </c>
       <c r="E47" s="3">
-        <v>210700</v>
+        <v>322300</v>
       </c>
       <c r="F47" s="3">
-        <v>195600</v>
+        <v>317200</v>
       </c>
       <c r="G47" s="3">
-        <v>187600</v>
+        <v>329100</v>
       </c>
       <c r="H47" s="3">
-        <v>132900</v>
+        <v>249700</v>
       </c>
       <c r="I47" s="3">
-        <v>152900</v>
+        <v>271700</v>
       </c>
       <c r="J47" s="3">
-        <v>200000</v>
+        <v>156500</v>
       </c>
       <c r="K47" s="3">
         <v>20800</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>499200</v>
+        <v>464900</v>
       </c>
       <c r="E48" s="3">
-        <v>993900</v>
+        <v>526500</v>
       </c>
       <c r="F48" s="3">
-        <v>445300</v>
+        <v>516500</v>
       </c>
       <c r="G48" s="3">
-        <v>481300</v>
+        <v>613000</v>
       </c>
       <c r="H48" s="3">
-        <v>482500</v>
+        <v>631600</v>
       </c>
       <c r="I48" s="3">
-        <v>235300</v>
+        <v>299000</v>
       </c>
       <c r="J48" s="3">
-        <v>567600</v>
+        <v>300000</v>
       </c>
       <c r="K48" s="3">
         <v>268100</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>203700</v>
+        <v>189600</v>
       </c>
       <c r="E49" s="3">
-        <v>375900</v>
+        <v>199200</v>
       </c>
       <c r="F49" s="3">
-        <v>183900</v>
+        <v>213300</v>
       </c>
       <c r="G49" s="3">
-        <v>163600</v>
+        <v>208300</v>
       </c>
       <c r="H49" s="3">
-        <v>173000</v>
+        <v>226400</v>
       </c>
       <c r="I49" s="3">
-        <v>176800</v>
+        <v>224700</v>
       </c>
       <c r="J49" s="3">
-        <v>231700</v>
+        <v>219800</v>
       </c>
       <c r="K49" s="3">
         <v>62400</v>
@@ -2368,26 +2368,26 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>141800</v>
-      </c>
-      <c r="E52" s="3">
-        <v>95800</v>
+      <c r="D52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F52" s="3">
-        <v>79100</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
-        <v>71800</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>63100</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
-        <v>62100</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3">
-        <v>247400</v>
+        <v>119700</v>
       </c>
       <c r="K52" s="3">
         <v>145300</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1943400</v>
+        <v>1809600</v>
       </c>
       <c r="E54" s="3">
-        <v>1748900</v>
+        <v>1852000</v>
       </c>
       <c r="F54" s="3">
-        <v>1645800</v>
+        <v>1908900</v>
       </c>
       <c r="G54" s="3">
-        <v>1567500</v>
+        <v>1996200</v>
       </c>
       <c r="H54" s="3">
-        <v>1466300</v>
+        <v>1919300</v>
       </c>
       <c r="I54" s="3">
-        <v>1187800</v>
+        <v>1509700</v>
       </c>
       <c r="J54" s="3">
-        <v>1101700</v>
+        <v>1444800</v>
       </c>
       <c r="K54" s="3">
         <v>926000</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>79100</v>
+        <v>168200</v>
       </c>
       <c r="E57" s="3">
-        <v>230700</v>
+        <v>167900</v>
       </c>
       <c r="F57" s="3">
-        <v>61900</v>
+        <v>170800</v>
       </c>
       <c r="G57" s="3">
-        <v>45400</v>
+        <v>174000</v>
       </c>
       <c r="H57" s="3">
-        <v>42400</v>
+        <v>170000</v>
       </c>
       <c r="I57" s="3">
-        <v>55500</v>
+        <v>198200</v>
       </c>
       <c r="J57" s="3">
-        <v>144700</v>
+        <v>140800</v>
       </c>
       <c r="K57" s="3">
         <v>98800</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>213900</v>
+        <v>199200</v>
       </c>
       <c r="E58" s="3">
-        <v>239000</v>
+        <v>126600</v>
       </c>
       <c r="F58" s="3">
-        <v>116200</v>
+        <v>134800</v>
       </c>
       <c r="G58" s="3">
-        <v>131800</v>
+        <v>167800</v>
       </c>
       <c r="H58" s="3">
-        <v>110600</v>
+        <v>144800</v>
       </c>
       <c r="I58" s="3">
-        <v>136800</v>
+        <v>173900</v>
       </c>
       <c r="J58" s="3">
-        <v>211600</v>
+        <v>140400</v>
       </c>
       <c r="K58" s="3">
         <v>94800</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>405300</v>
+        <v>282900</v>
       </c>
       <c r="E59" s="3">
-        <v>361000</v>
+        <v>291300</v>
       </c>
       <c r="F59" s="3">
-        <v>367000</v>
+        <v>326600</v>
       </c>
       <c r="G59" s="3">
-        <v>343000</v>
+        <v>320600</v>
       </c>
       <c r="H59" s="3">
-        <v>313300</v>
+        <v>295700</v>
       </c>
       <c r="I59" s="3">
-        <v>183400</v>
+        <v>105300</v>
       </c>
       <c r="J59" s="3">
-        <v>242100</v>
+        <v>86400</v>
       </c>
       <c r="K59" s="3">
         <v>75900</v>
@@ -2657,25 +2657,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>698300</v>
+        <v>650300</v>
       </c>
       <c r="E60" s="3">
-        <v>552800</v>
+        <v>585700</v>
       </c>
       <c r="F60" s="3">
-        <v>545100</v>
+        <v>632300</v>
       </c>
       <c r="G60" s="3">
-        <v>520100</v>
+        <v>662400</v>
       </c>
       <c r="H60" s="3">
-        <v>466400</v>
+        <v>610500</v>
       </c>
       <c r="I60" s="3">
-        <v>375600</v>
+        <v>477400</v>
       </c>
       <c r="J60" s="3">
-        <v>299200</v>
+        <v>396800</v>
       </c>
       <c r="K60" s="3">
         <v>269500</v>
@@ -2702,22 +2702,22 @@
         <v>300</v>
       </c>
       <c r="E61" s="3">
-        <v>25600</v>
+        <v>27100</v>
       </c>
       <c r="F61" s="3">
-        <v>39100</v>
+        <v>45300</v>
       </c>
       <c r="G61" s="3">
-        <v>49700</v>
+        <v>63300</v>
       </c>
       <c r="H61" s="3">
-        <v>86400</v>
+        <v>113100</v>
       </c>
       <c r="I61" s="3">
-        <v>181200</v>
+        <v>230200</v>
       </c>
       <c r="J61" s="3">
-        <v>187600</v>
+        <v>248800</v>
       </c>
       <c r="K61" s="3">
         <v>127300</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>342800</v>
+        <v>276400</v>
       </c>
       <c r="E62" s="3">
-        <v>546100</v>
+        <v>303200</v>
       </c>
       <c r="F62" s="3">
-        <v>318800</v>
+        <v>328400</v>
       </c>
       <c r="G62" s="3">
-        <v>351800</v>
+        <v>408300</v>
       </c>
       <c r="H62" s="3">
-        <v>345100</v>
+        <v>413500</v>
       </c>
       <c r="I62" s="3">
-        <v>83400</v>
+        <v>70800</v>
       </c>
       <c r="J62" s="3">
-        <v>158000</v>
+        <v>23800</v>
       </c>
       <c r="K62" s="3">
         <v>75100</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1050500</v>
+        <v>969800</v>
       </c>
       <c r="E66" s="3">
-        <v>909300</v>
+        <v>954500</v>
       </c>
       <c r="F66" s="3">
-        <v>910800</v>
+        <v>1047400</v>
       </c>
       <c r="G66" s="3">
-        <v>928800</v>
+        <v>1173700</v>
       </c>
       <c r="H66" s="3">
-        <v>904900</v>
+        <v>1175300</v>
       </c>
       <c r="I66" s="3">
-        <v>646200</v>
+        <v>813700</v>
       </c>
       <c r="J66" s="3">
-        <v>572500</v>
+        <v>748200</v>
       </c>
       <c r="K66" s="3">
         <v>476200</v>
@@ -3137,25 +3137,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>465900</v>
+        <v>433800</v>
       </c>
       <c r="E72" s="3">
-        <v>363500</v>
+        <v>384200</v>
       </c>
       <c r="F72" s="3">
-        <v>262900</v>
+        <v>304900</v>
       </c>
       <c r="G72" s="3">
-        <v>177800</v>
+        <v>226500</v>
       </c>
       <c r="H72" s="3">
-        <v>117200</v>
+        <v>153300</v>
       </c>
       <c r="I72" s="3">
-        <v>87600</v>
+        <v>111300</v>
       </c>
       <c r="J72" s="3">
-        <v>128400</v>
+        <v>79100</v>
       </c>
       <c r="K72" s="3">
         <v>30400</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>892800</v>
+        <v>831400</v>
       </c>
       <c r="E76" s="3">
-        <v>839500</v>
+        <v>888500</v>
       </c>
       <c r="F76" s="3">
-        <v>735000</v>
+        <v>852500</v>
       </c>
       <c r="G76" s="3">
-        <v>638700</v>
+        <v>813400</v>
       </c>
       <c r="H76" s="3">
-        <v>561400</v>
+        <v>734900</v>
       </c>
       <c r="I76" s="3">
-        <v>541500</v>
+        <v>688300</v>
       </c>
       <c r="J76" s="3">
-        <v>529200</v>
+        <v>689900</v>
       </c>
       <c r="K76" s="3">
         <v>449800</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>140800</v>
+        <v>131100</v>
       </c>
       <c r="E81" s="3">
-        <v>133800</v>
+        <v>141700</v>
       </c>
       <c r="F81" s="3">
-        <v>111300</v>
+        <v>129100</v>
       </c>
       <c r="G81" s="3">
-        <v>69000</v>
+        <v>87800</v>
       </c>
       <c r="H81" s="3">
-        <v>28400</v>
+        <v>37200</v>
       </c>
       <c r="I81" s="3">
-        <v>25000</v>
+        <v>31800</v>
       </c>
       <c r="J81" s="3">
-        <v>32400</v>
+        <v>48100</v>
       </c>
       <c r="K81" s="3">
         <v>21300</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>208000</v>
+        <v>193700</v>
       </c>
       <c r="E83" s="3">
-        <v>204500</v>
+        <v>216700</v>
       </c>
       <c r="F83" s="3">
-        <v>202000</v>
+        <v>234200</v>
       </c>
       <c r="G83" s="3">
-        <v>198600</v>
+        <v>252900</v>
       </c>
       <c r="H83" s="3">
-        <v>202500</v>
+        <v>265100</v>
       </c>
       <c r="I83" s="3">
-        <v>111000</v>
+        <v>141000</v>
       </c>
       <c r="J83" s="3">
-        <v>95200</v>
+        <v>81500</v>
       </c>
       <c r="K83" s="3">
         <v>73400</v>
@@ -3748,25 +3748,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>289500</v>
+        <v>269600</v>
       </c>
       <c r="E89" s="3">
-        <v>273600</v>
+        <v>289800</v>
       </c>
       <c r="F89" s="3">
-        <v>309400</v>
+        <v>358800</v>
       </c>
       <c r="G89" s="3">
-        <v>287900</v>
+        <v>366600</v>
       </c>
       <c r="H89" s="3">
-        <v>237100</v>
+        <v>310300</v>
       </c>
       <c r="I89" s="3">
-        <v>178600</v>
+        <v>227000</v>
       </c>
       <c r="J89" s="3">
-        <v>104100</v>
+        <v>124900</v>
       </c>
       <c r="K89" s="3">
         <v>49700</v>
@@ -3808,25 +3808,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-83400</v>
+        <v>-77600</v>
       </c>
       <c r="E91" s="3">
-        <v>-83700</v>
+        <v>-88700</v>
       </c>
       <c r="F91" s="3">
-        <v>-48200</v>
+        <v>-55900</v>
       </c>
       <c r="G91" s="3">
-        <v>-45400</v>
+        <v>-57800</v>
       </c>
       <c r="H91" s="3">
-        <v>-51100</v>
+        <v>-66900</v>
       </c>
       <c r="I91" s="3">
-        <v>-50300</v>
+        <v>-63900</v>
       </c>
       <c r="J91" s="3">
-        <v>-190700</v>
+        <v>-148500</v>
       </c>
       <c r="K91" s="3">
         <v>-71600</v>
@@ -3934,25 +3934,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-127300</v>
+        <v>-118500</v>
       </c>
       <c r="E94" s="3">
-        <v>-130500</v>
+        <v>-138300</v>
       </c>
       <c r="F94" s="3">
-        <v>-84100</v>
+        <v>-97500</v>
       </c>
       <c r="G94" s="3">
-        <v>-93800</v>
+        <v>-119500</v>
       </c>
       <c r="H94" s="3">
-        <v>-51600</v>
+        <v>-67500</v>
       </c>
       <c r="I94" s="3">
-        <v>-61700</v>
+        <v>-78400</v>
       </c>
       <c r="J94" s="3">
-        <v>-101500</v>
+        <v>-122800</v>
       </c>
       <c r="K94" s="3">
         <v>-49700</v>
@@ -3994,25 +3994,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-40300</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-34800</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-27200</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-10900</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-8600</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-8600</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>-8600</v>
+        <v>11500</v>
       </c>
       <c r="K96" s="3">
         <v>-7600</v>
@@ -4162,25 +4162,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-147700</v>
+        <v>-137500</v>
       </c>
       <c r="E100" s="3">
-        <v>-182700</v>
+        <v>-193600</v>
       </c>
       <c r="F100" s="3">
-        <v>-193800</v>
+        <v>-224800</v>
       </c>
       <c r="G100" s="3">
-        <v>-167700</v>
+        <v>-213500</v>
       </c>
       <c r="H100" s="3">
-        <v>-137400</v>
+        <v>-179900</v>
       </c>
       <c r="I100" s="3">
-        <v>-41800</v>
+        <v>-53100</v>
       </c>
       <c r="J100" s="3">
-        <v>-5100</v>
+        <v>-7000</v>
       </c>
       <c r="K100" s="3">
         <v>16800</v>
@@ -4204,25 +4204,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>6700</v>
+        <v>6300</v>
       </c>
       <c r="E101" s="3">
-        <v>4700</v>
+        <v>5000</v>
       </c>
       <c r="F101" s="3">
-        <v>3400</v>
+        <v>4000</v>
       </c>
       <c r="G101" s="3">
+        <v>800</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="H101" s="3">
-        <v>-400</v>
-      </c>
-      <c r="I101" s="3">
-        <v>400</v>
-      </c>
       <c r="J101" s="3">
-        <v>-500</v>
+        <v>-300</v>
       </c>
       <c r="K101" s="3">
         <v>-600</v>
@@ -4246,25 +4246,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>21300</v>
+        <v>19800</v>
       </c>
       <c r="E102" s="3">
-        <v>-34900</v>
+        <v>-37000</v>
       </c>
       <c r="F102" s="3">
-        <v>35000</v>
+        <v>40500</v>
       </c>
       <c r="G102" s="3">
-        <v>26900</v>
+        <v>34300</v>
       </c>
       <c r="H102" s="3">
-        <v>47700</v>
+        <v>62400</v>
       </c>
       <c r="I102" s="3">
-        <v>75500</v>
+        <v>96000</v>
       </c>
       <c r="J102" s="3">
-        <v>-3000</v>
+        <v>-5200</v>
       </c>
       <c r="K102" s="3">
         <v>16100</v>

--- a/AAII_Financials/Yearly/IIJIY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IIJIY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
   <si>
     <t>IIJIY</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44286</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43921</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43555</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43190</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42825</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42460</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42094</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41729</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41364</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2115800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1825300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1901000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1863900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1925900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1900300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1736600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1657600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1063500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1033800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1049600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1046700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>965800</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1659000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1403000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1465400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1438700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1561700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1597400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1475100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1391800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>893300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>852500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>861300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>853800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>767100</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>456800</v>
+      </c>
+      <c r="E10" s="3">
         <v>422200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>435600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>425100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>364200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>302900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>261500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>265800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>170200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>181200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>188300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>193000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>198600</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,50 +873,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="3">
         <v>4200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3700</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -944,77 +960,83 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3">
         <v>-100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-3200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-23400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-9000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>209500</v>
+      </c>
+      <c r="E15" s="3">
         <v>21800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>23200</v>
-      </c>
-      <c r="F15" s="3">
-        <v>25700</v>
       </c>
       <c r="G15" s="3">
         <v>25700</v>
       </c>
       <c r="H15" s="3">
+        <v>25700</v>
+      </c>
+      <c r="I15" s="3">
         <v>26400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>11500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>84900</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>10</v>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1914700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1633000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1697600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1668800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1792100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1819900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1679500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1594000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1029100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>988700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1006600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>994300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>895500</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>201000</v>
+      </c>
+      <c r="E18" s="3">
         <v>192300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>203400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>195000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>133800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>80400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>57100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>63700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>34400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>45000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>43000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>52400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>70300</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>16200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>7400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>7400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2800</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>404400</v>
+      </c>
+      <c r="E21" s="3">
         <v>214400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>227800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>204500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>157700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>99400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>66100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>151900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>112400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>119500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>129400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>141000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>141500</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>3700</v>
+      <c r="D22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E22" s="3">
         <v>3700</v>
       </c>
       <c r="F22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="G22" s="3">
         <v>4200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2600</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>194900</v>
+      </c>
+      <c r="E23" s="3">
         <v>191300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>205400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>199000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>126900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>66500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>52700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>75100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>36600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>45500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>43800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>57500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>70500</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E24" s="3">
         <v>59200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>62700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>68900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>38300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>27600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>19300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>25400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>15000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>16000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>16200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>16400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>23700</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>134300</v>
+      </c>
+      <c r="E26" s="3">
         <v>132100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>142800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>130100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>88600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>39000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>33400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>49700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>21600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>29500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>27700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>41000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>46800</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>133100</v>
+      </c>
+      <c r="E27" s="3">
         <v>131100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>141700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>129100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>87800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>37200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>31800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>48100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>21300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>29700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>28300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>41000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>48200</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1550,8 +1610,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>10</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>10</v>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-16200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-7400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-7400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2800</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>133100</v>
+      </c>
+      <c r="E33" s="3">
         <v>131100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>141700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>129100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>87800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>37200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>31800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>48100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>21300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>29700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>28300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>41000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>48200</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>133100</v>
+      </c>
+      <c r="E35" s="3">
         <v>131100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>141700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>129100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>87800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>37200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>31800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>48100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>21300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>29700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>28300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>41000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>48200</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44286</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43921</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43555</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43190</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42825</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42460</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42094</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41729</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41364</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,50 +1986,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>217300</v>
+      </c>
+      <c r="E41" s="3">
         <v>300600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>319500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>390300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>384000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>359400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>288400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>201500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>148000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>143800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>179900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>205400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>111400</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1969,8 +2058,8 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>10</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>10</v>
@@ -1984,303 +2073,327 @@
       <c r="O42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>376400</v>
+      </c>
+      <c r="E43" s="3">
         <v>302000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>311000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>310000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>314600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>306500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>301200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>299700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>184500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>174400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>189800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>176000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>170500</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E44" s="3">
         <v>21300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>24000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>21500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>19600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>23000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>30700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>16100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>18900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>14700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>10500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>15300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>11800</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>56700</v>
+      </c>
+      <c r="E45" s="3">
         <v>35800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>32600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>27100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>30500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>25700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>15500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>35700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>78200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>59600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>64100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>76900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>46600</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>869400</v>
+      </c>
+      <c r="E46" s="3">
         <v>792600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>802500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>860400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>844500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>804700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>712700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>632600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>429500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>392500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>444300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>473600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>340300</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>475000</v>
+      </c>
+      <c r="E47" s="3">
         <v>360600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>322300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>317200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>329100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>249700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>271700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>156500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>20800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>21400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>21000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>18500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>14600</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>531100</v>
+      </c>
+      <c r="E48" s="3">
         <v>464900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>526500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>516500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>613000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>631600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>299000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>300000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>268100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>252300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>250500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>247100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>209300</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>209200</v>
+      </c>
+      <c r="E49" s="3">
         <v>189600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>199200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>213300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>208300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>226400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>224700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>219800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>62400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>71400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>86200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>94400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>97800</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,9 +2478,12 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2374,8 +2493,8 @@
       <c r="E52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
+      <c r="F52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
@@ -2387,26 +2506,29 @@
         <v>0</v>
       </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>119700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>145300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>128400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>125100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>117800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>84300</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2086400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1809600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1852000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1908900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1996200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1919300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1509700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1444800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>926000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>866100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>927300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>951400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>746400</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>201900</v>
+      </c>
+      <c r="E57" s="3">
         <v>168200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>167900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>170800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>174000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>170000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>198200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>140800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>98800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>102200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>103900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>105300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>99700</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>224500</v>
+      </c>
+      <c r="E58" s="3">
         <v>199200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>126600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>134800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>167800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>144800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>173900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>140400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>94800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>97100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>108900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>129500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>126500</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>330300</v>
+      </c>
+      <c r="E59" s="3">
         <v>282900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>291300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>326600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>320600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>295700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>105300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>86400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>75900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>65800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>74900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>62700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>68100</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>756700</v>
+      </c>
+      <c r="E60" s="3">
         <v>650300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>585700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>632300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>662400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>610500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>477400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>396800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>269500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>265100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>287800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>297400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>294400</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>27100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>45300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>63300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>113100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>230200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>248800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>127300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>57200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>37000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>42200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>57700</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>338600</v>
+      </c>
+      <c r="E62" s="3">
         <v>276400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>303200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>328400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>408300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>413500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>70800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>23800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>75100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>63500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>66400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>60600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>52200</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1137600</v>
+      </c>
+      <c r="E66" s="3">
         <v>969800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>954500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1047400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1173700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1175300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>813700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>748200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>476200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>389500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>394100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>402600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>404500</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>533500</v>
+      </c>
+      <c r="E72" s="3">
         <v>433800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>384200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>304900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>226500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>153300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>111300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>79100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>30400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>18200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-4700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-26300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-58200</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>939500</v>
+      </c>
+      <c r="E76" s="3">
         <v>831400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>888500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>852500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>813400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>734900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>688300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>689900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>449800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>476600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>533200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>548800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>341800</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44286</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43921</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43555</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43190</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42825</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42460</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42094</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41729</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41364</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>133100</v>
+      </c>
+      <c r="E81" s="3">
         <v>131100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>141700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>129100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>87800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>37200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>31800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>48100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>21300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>29700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>28300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>41000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>48200</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>209500</v>
+      </c>
+      <c r="E83" s="3">
         <v>193700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>216700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>234200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>252900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>265100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>141000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>81500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>73400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>72900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>82500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>80800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>68200</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>190500</v>
+      </c>
+      <c r="E89" s="3">
         <v>269600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>289800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>358800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>366600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>310300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>227000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>124900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>49700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>88600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>110100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>80500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>88700</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-79500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-77600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-88700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-55900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-57800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-66900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-63900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-148500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-71600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-80100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-69600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-83600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-50800</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-145200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-118500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-138300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-97500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-119500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-67500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-78400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-122800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-49700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-61600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-68900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-93500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-54000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,8 +4220,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4012,26 +4245,29 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>11500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-7600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-7400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-8600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-8300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-6400</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-131300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-137500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-193600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-224800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-213500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-179900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-53100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>16800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-38200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-53600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>104300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-45400</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
         <v>6300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>5000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>4000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-600</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-800</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-86400</v>
+      </c>
+      <c r="E102" s="3">
         <v>19800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-37000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>40500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>34300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>62400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>96000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>16100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-11200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-11300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>93100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-11600</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/IIJIY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IIJIY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
   <si>
     <t>IIJIY</t>
   </si>
@@ -879,8 +879,8 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>10</v>
+      <c r="D12" s="3">
+        <v>4300</v>
       </c>
       <c r="E12" s="3">
         <v>4200</v>
@@ -969,8 +969,8 @@
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>10</v>
+      <c r="D14" s="3">
+        <v>-700</v>
       </c>
       <c r="E14" s="3">
         <v>-100</v>
@@ -1015,7 +1015,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>209500</v>
+        <v>24300</v>
       </c>
       <c r="E15" s="3">
         <v>21800</v>
@@ -1076,7 +1076,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1914700</v>
+        <v>1914600</v>
       </c>
       <c r="E17" s="3">
         <v>1633000</v>
@@ -1121,7 +1121,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>201000</v>
+        <v>201200</v>
       </c>
       <c r="E18" s="3">
         <v>192300</v>
@@ -1185,7 +1185,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>6100</v>
+        <v>2600</v>
       </c>
       <c r="E20" s="3">
         <v>-300</v>
@@ -1230,7 +1230,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>404400</v>
+        <v>222900</v>
       </c>
       <c r="E21" s="3">
         <v>214400</v>
@@ -1274,8 +1274,8 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>10</v>
+      <c r="D22" s="3">
+        <v>6600</v>
       </c>
       <c r="E22" s="3">
         <v>3700</v>
@@ -1725,7 +1725,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-6100</v>
+        <v>-2600</v>
       </c>
       <c r="E32" s="3">
         <v>300</v>
